--- a/docs/greyin-requirements-traceability.xlsx
+++ b/docs/greyin-requirements-traceability.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F105"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -1174,79 +1174,79 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>DeepEdge</v>
+        <v>Greyin Hub</v>
       </c>
       <c r="B39" t="str">
-        <v>Jobs &amp; Applications</v>
+        <v>Admin</v>
       </c>
       <c r="C39" t="str">
-        <v>FR-EE-01</v>
+        <v>FR-PW-38</v>
       </c>
       <c r="D39" t="str">
-        <v>Employers can post/edit jobs; candidates can browse, filter, and apply with a cover letter</v>
+        <v>A visible "Admin" card on the Hub's own /dashboard, linking to /admin, shown only when profiles.role='admin'. Found via a direct user question ("why am I not seeing admin panel on login? am I missing something") about their own real admin@greyin.net account -- confirmed the account and /admin route both worked correctly, but the Hub was the one app with genuinely no link to its own admin panel anywhere (header or dashboard), unlike 5 of the 6 pillar apps, each of which surfaces its own pillar-specific /admin the same way on their dashboard already. Longlist, the 6th pillar app, was checked too and correctly has no such card -- it has no /admin route of its own at all, since platform-wide admin was deliberately consolidated on the Hub alone (see admin/page.tsx's own header comment), not duplicated per pillar.</v>
       </c>
       <c r="E39" t="str">
-        <v>001, 003</v>
+        <v>none</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>DeepEdge</v>
+        <v>Greyin Hub</v>
       </c>
       <c r="B40" t="str">
-        <v>Jobs &amp; Applications</v>
+        <v>Dashboard</v>
       </c>
       <c r="C40" t="str">
-        <v>FR-EE-02</v>
+        <v>FR-PW-39</v>
       </c>
       <c r="D40" t="str">
-        <v>Employers can review applications and update status; candidates see status changes</v>
+        <v>The Hub dashboard's "Activity across all six platforms" heatmap now genuinely covers all six -- my_pillar_activity (046_pillar_activity_view.sql) only ever unioned deepedge/flexpro/stackworks/saltnpepper/greymatters; Longlist launched later and was never added as a source, so a real future-role post or future-interested subscription never appeared for anyone, structurally, not as a display bug. Found via a direct user report ("dashboard not showing any activity on longlist"). Fixed in 108_pillar_activity_longlist.sql (two new UNION branches: future_roles.posted_by as role_posted, future_role_subscriptions.user_id as role_subscribed) and verified against a real seeded user's real future-role post (0 activities -&gt; 3, correctly attributed). Found and fixed in the same pass, unprompted: ActivityHeatmap.tsx's own PILLAR_COLORS/PILLAR_LABELS map still keyed DeepEdge as 'expertedge' (the pre-2026-09-03-rename identifier, fixed DB-side in migration 106 but never updated in this one frontend file), so DeepEdge's own activity squares had been silently rendering colorless -- indistinguishable from "no activity" -- since that rename shipped, despite the correct total count showing.</v>
       </c>
       <c r="E40" t="str">
-        <v>001, 017</v>
+        <v>108</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DeepEdge</v>
+        <v>Platform-Wide</v>
       </c>
       <c r="B41" t="str">
-        <v>Company Profiles</v>
+        <v>Theming</v>
       </c>
       <c r="C41" t="str">
-        <v>FR-EE-03</v>
+        <v>FR-PW-40</v>
       </c>
       <c r="D41" t="str">
-        <v>A public company directory page lists open positions per company</v>
+        <v>Foundation pass (2026-09-04) of a real light/dark mode toggle across all 7 apps (the 6 pillars plus the Hub), at explicit user request ("implement light/dark mode themes for overall site viewing and validate theme changes for all pages"), scoped per the user's own selected approach ("Foundation first, then expand"): build the real infrastructure and apply it thoroughly to shared chrome and each app's homepage first, rather than a shallow pass over every page at once. Infrastructure: Tailwind darkMode:'class' in all 7 tailwind.config.js; a duplicated-per-app ThemeToggle.tsx (localStorage key greyin:theme, matching this platform's established per-app-component convention) toggling a .dark class on &lt;html&gt;; a synchronous inline &lt;script&gt; in each layout.tsx's own &lt;head&gt;, applying the persisted choice (or, absent one, the OS prefers-color-scheme) before first paint, so there is no flash from light to dark for a returning dark-mode visitor -- a plain useEffect-driven toggle alone would run after the browser had already painted the server-rendered light-mode HTML once. Applied with dark: variants throughout each app's SiteHeader (incl. dark:brightness-0 dark:invert on the Hub's fixed-dark-navy logo assets, the same technique SiteFooter.tsx already used unconditionally), IdleSessionGuard's modal, and each app's own homepage; SiteFooter and the PreviewBanner were already permanently dark surfaces and are left theme-invariant by deliberate choice rather than given a light variant with no benefit over what already renders correctly in both themes. Verified live in production, not just locally: typecheck + build clean on all 7 apps, then deployed (docker build + service update --force, all 7), then a real Playwright pass against all 7 live domains confirmed the toggle is present, clicking it applies .dark (body background genuinely changes to gray-950), and the choice survives a full page reload via localStorage -- plus a visual screenshot comparison (Hub, DeepEdge, Longlist) confirming legible contrast and correct logo/icon inversion, not just a computed-style check. Deliberately incomplete by design, not oversight: inner pages (dashboards, admin panels, job/candidate/gig listings, forms, detail pages -- upwards of 150 pages combined across all 7 apps) are unstyled for dark mode and still render their light-mode palette regardless of the toggle; a page-by-page follow-up pass is the explicitly agreed next step, not yet started.</v>
       </c>
       <c r="E41" t="str">
-        <v>001</v>
+        <v>none</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DeepEdge</v>
+        <v>Platform-Wide</v>
       </c>
       <c r="B42" t="str">
-        <v>Company Reviews</v>
+        <v>Theming</v>
       </c>
       <c r="C42" t="str">
-        <v>FR-EE-04</v>
+        <v>FR-PW-41</v>
       </c>
       <c r="D42" t="str">
-        <v>Only candidates with a real application on record at a company may leave a 1-5 star + text review of that company</v>
+        <v>Follow-up pass (2026-09-04, same day) completing FR-PW-40's explicitly-deferred inner-page work, at direct user request ("take up the followup pass for inner pages"): all 169 page.tsx files across all 7 apps now carry dark: variants, not just shared chrome and each homepage. Given the scale, applied via a purpose-built, tested-before-rollout script (not hand-editing 169 files) that (1) walks every className="..." and static className={`...`} attribute for a fixed light-neutral -&gt; dark-neutral and 17-accent-color -&gt; dark-accent mapping matching the exact palette already hand-crafted in FR-PW-40 (e.g. bg-white-&gt;dark:bg-gray-900, text-gray-600-&gt;dark:text-gray-400, bg-indigo-50-&gt;dark:bg-indigo-950/40), (2) separately darkifies plain string literals that are themselves class-lists rather than inline JSX attributes -- ternary branches inside a template-literal className and STATUS_STYLES-style lookup objects keyed by e.g. application/outcome status, gated behind a strict Tailwind-prefix heuristic so it does not touch unrelated string literals, and (3) adds a dark bg/text fallback to any &lt;input&gt;/&lt;textarea&gt;/&lt;select&gt; with no explicit background class, so form fields do not render as a stray white box on a dark page. Incidentally discovered and separately addressed in this same pass: ~99 of 169 pages across the 6 pillar apps (not the Hub, which is fully consistent) render their own one-off inline &lt;header&gt; instead of importing the shared SiteHeader component -- a pre-existing structural inconsistency, not caused by this work -- so those pages had no local theme-toggle control even though their styling correctly followed a theme already toggled elsewhere (confirmed live: toggling on a page with the real header and then navigating to an inline-header page correctly carries dark mode over via the persisted .dark class and localStorage choice from FR-PW-40). Added a ThemeToggle to 73 of those 89 addressable inline headers via 3 targeted structural patterns (a back-link+title+empty-spacer layout, a brand-only flex row, and an existing icon-action row) verified individually before bulk rollout; the remaining ~16 pages with more bespoke header layouts still render dark mode correctly if already toggled elsewhere, they just have no local switch on that specific page -- left for a future pass rather than force-fitting a risky insertion. Verified against real production, not just locally: typecheck + build clean on all 7 apps (twice -- once after the bulk class pass, again after the toggle-insertion pass), deployed both rounds (docker build + service update --force), and Playwright-verified live: toggling on one page and navigating to an inline-header page confirmed the .dark class and gray-950 background genuinely carry over; a newly-toggle-equipped page (Longlist /terms) screenshotted in both themes end-to-end, legible and correctly placed.</v>
       </c>
       <c r="E42" t="str">
-        <v>058</v>
+        <v>none</v>
       </c>
       <c r="F42" t="str">
         <v>2026-08-23</v>
@@ -1254,19 +1254,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DeepEdge</v>
+        <v>Platform-Wide</v>
       </c>
       <c r="B43" t="str">
-        <v>Company Reviews</v>
+        <v>Theming</v>
       </c>
       <c r="C43" t="str">
-        <v>FR-EE-05</v>
+        <v>FR-PW-42</v>
       </c>
       <c r="D43" t="str">
-        <v>Company reviews are anonymous in display — reviewer identity is never rendered, only rating/text/date</v>
+        <v>Closed FR-PW-41's disclosed 16-page gap the same day, at direct user request ("address that as well"): the remaining inline-header pages that hadn't matched any of the 3 original insertion patterns (deepedge: subscribe, references/respond, employer/dashboard, enterprise-contact; flexpro: subscribe, orders, orders/[id], gigs/[id], sellers/[id], checkout/[id], client-jobs/[id]/pay/[orderId], mentor-sessions/checkout/[orderId]; saltnpepper: members; greymatters: search, categories, posts/[slug]) now all carry the toggle too -- 4 fixed by hand (each had a distinct enough header shape not worth generalizing: a bare single-Link div with no flex wrapper needing one added, a hardcoded deepedge.greyin.net brand href the original brand-only-row pattern didn't match, and a dashboard icon row whose last item was a Settings link rather than the Profile link the original pattern looked for), 12 by extending the same script with two more generalized structural patterns covering the two shapes that repeated across the rest (a single-Link-only header with no existing flex/justify wrapper, and a brand-row with a plain sibling &lt;nav&gt; the original brand-only pattern excluded) -- both tested on one sample file each before the 12-file rollout, matching this session's own established discipline. Inline-header toggle coverage is now 89/89 (100%), up from 73/89. Verified: typecheck + build clean on all 4 touched apps, deployed (docker build + service update --force), and Playwright-confirmed live on the 3 previously-failing pages reachable without auth (saltnpepper /members, greymatters /categories and /search); the other 4 fixed pages are auth-gated and redirect anonymous requests to /login, so they were verified via clean typecheck/build and direct source inspection (import + JSX both present) rather than a live authenticated screenshot, which would have needed a full signup+email-verification flow for marginal extra confidence over what a Next.js build failure would already have caught.</v>
       </c>
       <c r="E43" t="str">
-        <v>058</v>
+        <v>none</v>
       </c>
       <c r="F43" t="str">
         <v>2026-08-23</v>
@@ -1274,22 +1274,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>DeepEdge</v>
+        <v>Platform-Wide</v>
       </c>
       <c r="B44" t="str">
-        <v>Resume &amp; Employment History</v>
+        <v>Theming</v>
       </c>
       <c r="C44" t="str">
-        <v>FR-EE-06</v>
+        <v>FR-PW-43</v>
       </c>
       <c r="D44" t="str">
-        <v>Candidates can upload/parse a resume and maintain a structured employment history (past roles, dates, past/expected salary)</v>
+        <v>Three same-day follow-ups after FR-PW-42, at direct user request ("wat next" -&gt; picked all three offered options): (1) added the first permanent e2e regression coverage for the toggle itself, tests/cross-platform/dark-mode-toggle.spec.ts, parameterized across all 7 domains -- checks the toggle is present after hydration, clicking it adds .dark and genuinely changes the rendered body background (not just an aria-label flip), the choice survives a full reload via localStorage, and toggling back returns to light; every prior check across FR-PW-40/41/42 had been a one-off manual Playwright script, discarded after each run. (2) Fixed a real, pre-existing bug found incidentally during FR-PW-41's own local build (unrelated to dark mode): greymatters-blog's /rss.xml route treated any postsRes.json() that resolved to a well-formed non-array body (a PostgREST error object on a non-2xx response, most commonly) the same as a successful post list, since .catch(() =&gt; []) only guards a JSON *parse* failure -- posts.map() then threw. Fixed by gating on both postsRes.ok and Array.isArray(body) so any failure mode degrades to an empty feed instead of a crash; confirmed fixed both by a clean local build (the route now prerenders successfully where it previously errored) and a live curl against the redeployed feed. (3) A visual spot-check of dark mode across a wider page sample surfaced a real, more consequential gap the original inner-page pass had missed entirely: bg-gradient-to-br soft pastel page-background washes (from-indigo-50, to-slate-100, etc.) never got dark: variants at all, because FR-PW-41's className mapping only covered bg-*/text-*/border-* utilities, not the separate from-*/via-*/to-* gradient-stop family -- every app's own /login, /signup, /reset-password, and /verify page (the highest-traffic unauthenticated pages on the entire platform) rendered a bright, untouched pastel background with dark-styled text on top of it whenever dark mode was already active from elsewhere. Fixed across all 40 affected non-homepage files by extending the same darkify.py script with a new from-/via-/to- mapping (collapsing every soft pastel stop to near-black grays, matching the exact simplification already used by hand on each app's own homepage hero gradient) -- verified live via a real screenshot of the redeployed /login page in forced-dark state. Self-caused-and-fixed regression along the way: the first attempt at this gradient fix used a file-exclusion pattern with a leading "/" that never matched relative paths, so it silently re-ran the *entire* mapping (not just the new gradient one) against all 7 already-hand-crafted homepages, appending a second, conflicting dark: color value alongside several already-correct hand-picked ones on the same elements (e.g. both dark:text-orange-500 and dark:text-orange-400 present together) -- caught before deployment by reviewing the actual diff the tool surfaced, not discovered live; written a small dedupe pass (drop any later dark: token sharing an earlier one's color family on the same className) and confirmed zero such conflicts remain platform-wide via a full-codebase scan before this round's build/deploy.</v>
       </c>
       <c r="E44" t="str">
-        <v>029, 055</v>
+        <v>none</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="45">
@@ -1297,19 +1297,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B45" t="str">
-        <v>Candidate Search</v>
+        <v>Jobs &amp; Applications</v>
       </c>
       <c r="C45" t="str">
-        <v>FR-EE-07</v>
+        <v>FR-EE-01</v>
       </c>
       <c r="D45" t="str">
-        <v>Employers with an active subscription can search the candidate database; the public candidate profile itself stays open (skills/endorsements/recommendations only)</v>
+        <v>Employers can post/edit jobs; candidates can browse, filter, and apply with a cover letter</v>
       </c>
       <c r="E45" t="str">
-        <v>039</v>
+        <v>001, 003</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="46">
@@ -1317,19 +1317,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B46" t="str">
-        <v>Subscriptions</v>
+        <v>Jobs &amp; Applications</v>
       </c>
       <c r="C46" t="str">
-        <v>FR-EE-08</v>
+        <v>FR-EE-02</v>
       </c>
       <c r="D46" t="str">
-        <v>Employers subscribe via Razorpay to unlock candidate search and enterprise features</v>
+        <v>Employers can review applications and update status; candidates see status changes</v>
       </c>
       <c r="E46" t="str">
-        <v>002, 039</v>
+        <v>001, 017</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="47">
@@ -1337,19 +1337,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B47" t="str">
-        <v>Enterprise</v>
+        <v>Company Profiles</v>
       </c>
       <c r="C47" t="str">
-        <v>FR-EE-09</v>
+        <v>FR-EE-03</v>
       </c>
       <c r="D47" t="str">
-        <v>Enterprise solutions intake and dedicated support workflow for large employers</v>
+        <v>A public company directory page lists open positions per company</v>
       </c>
       <c r="E47" t="str">
-        <v>044</v>
+        <v>001</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-06</v>
       </c>
     </row>
     <row r="48">
@@ -1357,19 +1357,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B48" t="str">
-        <v>Governance</v>
+        <v>Company Reviews</v>
       </c>
       <c r="C48" t="str">
-        <v>FR-EE-10</v>
+        <v>FR-EE-04</v>
       </c>
       <c r="D48" t="str">
-        <v>Verified-expert members can vote on the Verified Expert gate’s eligibility threshold (voting itself stays on greyin-b2b/governance/threshold; the admin-facing vote summary + live gate-settings editor moved to Greyin Hub's /admin/threshold-votes 2026-08-24 — see FR-PW platform admin)</v>
+        <v>Only candidates with a real application on record at a company may leave a 1-5 star + text review of that company</v>
       </c>
       <c r="E48" t="str">
-        <v>041</v>
+        <v>058</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="49">
@@ -1377,19 +1377,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B49" t="str">
-        <v>Job Alerts</v>
+        <v>Company Reviews</v>
       </c>
       <c r="C49" t="str">
-        <v>FR-EE-11</v>
+        <v>FR-EE-05</v>
       </c>
       <c r="D49" t="str">
-        <v>Candidates can subscribe to job alerts matching saved search criteria</v>
+        <v>Company reviews are anonymous in display — reviewer identity is never rendered, only rating/text/date</v>
       </c>
       <c r="E49" t="str">
-        <v>023</v>
+        <v>058</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="50">
@@ -1397,19 +1397,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B50" t="str">
-        <v>Enterprise</v>
+        <v>Resume &amp; Employment History</v>
       </c>
       <c r="C50" t="str">
-        <v>FR-EE-12</v>
+        <v>FR-EE-06</v>
       </c>
       <c r="D50" t="str">
-        <v>Fractional Leadership Placement: a sales-led, invoiced (not self-serve) enterprise offering -- /solutions markets it, /enterprise-contact?service=fractional_leadership captures the lead into the shared enterprise_leads pipeline (039), admin triages without a self-serve Activate action. Found during a full code sweep for features shipped but never tracked here -- real and tested, just never given its own FR row</v>
+        <v>Candidates can upload/parse a resume and maintain a structured employment history (past roles, dates, past/expected salary)</v>
       </c>
       <c r="E50" t="str">
-        <v>039, 044</v>
+        <v>029, 055</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="51">
@@ -1417,19 +1417,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B51" t="str">
-        <v>Enterprise</v>
+        <v>Candidate Search</v>
       </c>
       <c r="C51" t="str">
-        <v>FR-EE-13</v>
+        <v>FR-EE-07</v>
       </c>
       <c r="D51" t="str">
-        <v>Outplacement: a sales-led, invoiced (not self-serve), per-headcount enterprise offering for companies going through a layoff or restructuring -- connects departing employees into the Verified Expert ecosystem rather than a generic resume workshop. Same enterprise_leads pipeline and admin triage as FR-EE-12. One of Greyin's three Primary (revenue) tiers alongside Coaching (FR-PW-19/20) and the Longlist Future Hiring Pipeline (FR-LL-01/02) -- found during the same code sweep, real and tested, never tracked here until now</v>
+        <v>Employers with an active subscription can search the candidate database; the public candidate profile itself stays open (skills/endorsements/recommendations only)</v>
       </c>
       <c r="E51" t="str">
-        <v>039, 044</v>
+        <v>039</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="52">
@@ -1437,19 +1437,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B52" t="str">
-        <v>Jobs &amp; Applications</v>
+        <v>Subscriptions</v>
       </c>
       <c r="C52" t="str">
-        <v>FR-EE-14</v>
+        <v>FR-EE-08</v>
       </c>
       <c r="D52" t="str">
-        <v>A candidate can withdraw their own application (status -&gt; 'withdrawn'), one-way, from any non-terminal status. Emergent gap audit item #2 -- the 'withdrawn' enum value and its UI styling already existed but no RLS policy or route ever let a candidate set it, only the employer could update application status at all. The employer is notified when it happens</v>
+        <v>Employers subscribe via Razorpay to unlock candidate search and enterprise features</v>
       </c>
       <c r="E52" t="str">
-        <v>092</v>
+        <v>002, 039</v>
       </c>
       <c r="F52" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="53">
@@ -1457,19 +1457,19 @@
         <v>DeepEdge</v>
       </c>
       <c r="B53" t="str">
-        <v>Jobs &amp; Applications</v>
+        <v>Enterprise</v>
       </c>
       <c r="C53" t="str">
-        <v>FR-EE-15</v>
+        <v>FR-EE-09</v>
       </c>
       <c r="D53" t="str">
-        <v>An employer can close and reopen their own job listing without admin involvement (previously admin-only close, no reopen route at all -- Emergent gap audit item #1, its "most-impactful known issue"). Closing removes the job from the public /jobs listing and notifies every candidate with a still-open (non-terminal) application that the role has closed</v>
+        <v>Enterprise solutions intake and dedicated support workflow for large employers</v>
       </c>
       <c r="E53" t="str">
-        <v>092</v>
+        <v>044</v>
       </c>
       <c r="F53" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="54">
@@ -1477,213 +1477,213 @@
         <v>DeepEdge</v>
       </c>
       <c r="B54" t="str">
-        <v>Monetization</v>
+        <v>Governance</v>
       </c>
       <c r="C54" t="str">
-        <v>FR-EE-16</v>
+        <v>FR-EE-10</v>
       </c>
       <c r="D54" t="str">
-        <v>The single fixed Starter candidate-search plan is replaced with 3 admin-priced self-serve hiring tiers (Basic/Pro/Premium, subscription_tiers, product=deepedge_hiring), each carrying named monthly credit allowances an admin sets from /admin/subscription-tiers: job_post, profile_view, contact_view, job_invite, outplacement_post, placement_request (-1=unlimited, 0=withheld from that tier). Only profile_view is wired to a live enforcement point this pass -- consume_credit() gates the new /candidates/[id] full-profile view, a second, deeper gate layered on top of the pre-existing binary "any active subscription" gate on the /candidates search list itself, which is unchanged. job_post is deliberately left unenforced: job posting is free by a prior, deliberate hybrid-gate decision (038/039, to preserve open-board liquidity) and reversing that was not confirmed with the user. contact_view/job_invite/outplacement_post/placement_request are priced and admin-configurable but have no corresponding feature built yet to consume them (outplacement today is FR-EE-13's sales-led lead-capture form, not a self-serve post) -- flagged inline in the admin UI itself ("not yet enforced"), not silently implied as live. Sales-led Enterprise activation (FR-EE-12/13's admin Activate action) grants the unlimited Premium hiring tier automatically</v>
+        <v>Verified-expert members can vote on the Verified Expert gate’s eligibility threshold (voting itself stays on greyin-b2b/governance/threshold; the admin-facing vote summary + live gate-settings editor moved to Greyin Hub's /admin/threshold-votes 2026-08-24 — see FR-PW platform admin)</v>
       </c>
       <c r="E54" t="str">
-        <v>096</v>
+        <v>041</v>
       </c>
       <c r="F54" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>GreyMatters</v>
+        <v>DeepEdge</v>
       </c>
       <c r="B55" t="str">
-        <v>Blogging / CMS</v>
+        <v>Job Alerts</v>
       </c>
       <c r="C55" t="str">
-        <v>FR-GM-01</v>
+        <v>FR-EE-11</v>
       </c>
       <c r="D55" t="str">
-        <v>Verified authors (12+ years experience) can write, edit, and publish long-form posts with categories/tags</v>
+        <v>Candidates can subscribe to job alerts matching saved search criteria</v>
       </c>
       <c r="E55" t="str">
-        <v>030</v>
+        <v>023</v>
       </c>
       <c r="F55" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>GreyMatters</v>
+        <v>DeepEdge</v>
       </c>
       <c r="B56" t="str">
-        <v>Blogging / CMS</v>
+        <v>Enterprise</v>
       </c>
       <c r="C56" t="str">
-        <v>FR-GM-02</v>
+        <v>FR-EE-12</v>
       </c>
       <c r="D56" t="str">
-        <v>Readers can comment on posts; anonymous posting is supported for sensitive topics</v>
+        <v>Fractional Leadership Placement: a sales-led, invoiced (not self-serve) enterprise offering -- /solutions markets it, /enterprise-contact?service=fractional_leadership captures the lead into the shared enterprise_leads pipeline (039), admin triages without a self-serve Activate action. Found during a full code sweep for features shipped but never tracked here -- real and tested, just never given its own FR row</v>
       </c>
       <c r="E56" t="str">
-        <v>027</v>
+        <v>039, 044</v>
       </c>
       <c r="F56" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>GreyMatters</v>
+        <v>DeepEdge</v>
       </c>
       <c r="B57" t="str">
-        <v>Monetization</v>
+        <v>Enterprise</v>
       </c>
       <c r="C57" t="str">
-        <v>FR-GM-03</v>
+        <v>FR-EE-13</v>
       </c>
       <c r="D57" t="str">
-        <v>Readers can tip authors for valued posts</v>
+        <v>Outplacement: a sales-led, invoiced (not self-serve), per-headcount enterprise offering for companies going through a layoff or restructuring -- connects departing employees into the Verified Expert ecosystem rather than a generic resume workshop. Same enterprise_leads pipeline and admin triage as FR-EE-12. One of Greyin's three Primary (revenue) tiers alongside Coaching (FR-PW-19/20) and the Longlist Future Hiring Pipeline (FR-LL-01/02) -- found during the same code sweep, real and tested, never tracked here until now</v>
       </c>
       <c r="E57" t="str">
-        <v>026</v>
+        <v>039, 044</v>
       </c>
       <c r="F57" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>GreyMatters</v>
+        <v>DeepEdge</v>
       </c>
       <c r="B58" t="str">
-        <v>AI Quality</v>
+        <v>Jobs &amp; Applications</v>
       </c>
       <c r="C58" t="str">
-        <v>FR-GM-04</v>
+        <v>FR-EE-14</v>
       </c>
       <c r="D58" t="str">
-        <v>An LLM-based post-quality score sweeps published posts on a configurable interval</v>
+        <v>A candidate can withdraw their own application (status -&gt; 'withdrawn'), one-way, from any non-terminal status. Emergent gap audit item #2 -- the 'withdrawn' enum value and its UI styling already existed but no RLS policy or route ever let a candidate set it, only the employer could update application status at all. The employer is notified when it happens</v>
       </c>
       <c r="E58" t="str">
-        <v>048, 050</v>
+        <v>092</v>
       </c>
       <c r="F58" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>GreyMatters</v>
+        <v>DeepEdge</v>
       </c>
       <c r="B59" t="str">
-        <v>Newsletter</v>
+        <v>Jobs &amp; Applications</v>
       </c>
       <c r="C59" t="str">
-        <v>FR-GM-05</v>
+        <v>FR-EE-15</v>
       </c>
       <c r="D59" t="str">
-        <v>Visitors can subscribe to a newsletter digest of new posts</v>
+        <v>An employer can close and reopen their own job listing without admin involvement (previously admin-only close, no reopen route at all -- Emergent gap audit item #1, its "most-impactful known issue"). Closing removes the job from the public /jobs listing and notifies every candidate with a still-open (non-terminal) application that the role has closed</v>
       </c>
       <c r="E59" t="str">
-        <v>008</v>
+        <v>092</v>
       </c>
       <c r="F59" t="str">
-        <v>2026-08-07</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>GreyMatters</v>
+        <v>DeepEdge</v>
       </c>
       <c r="B60" t="str">
-        <v>Newsletter</v>
+        <v>Monetization</v>
       </c>
       <c r="C60" t="str">
-        <v>FR-GM-06</v>
+        <v>FR-EE-16</v>
       </c>
       <c r="D60" t="str">
-        <v>An admin can trigger a real email send (not just the in-app digest) to every newsletter subscriber, covering posts published in the last 7 days -- distinct from FR-RM-06's cross-pillar in-app digest, which deliberately skipped real email given the known SMTP rate-limit constraint; this one already sends real email at GreyMatters' own subscriber volume. Found during a full code sweep -- real, tested, never given its own FR row until now</v>
+        <v>The single fixed Starter candidate-search plan is replaced with 3 admin-priced self-serve hiring tiers (Basic/Pro/Premium, subscription_tiers, product=deepedge_hiring), each carrying named monthly credit allowances an admin sets from /admin/subscription-tiers: job_post, profile_view, contact_view, job_invite, outplacement_post, placement_request (-1=unlimited, 0=withheld from that tier). profile_view and, as of 2026-09-04 (109_grandfather_job_post_credits.sql), job_post are both wired to live enforcement -- consume_credit() gates the new /candidates/[id] full-profile view (a second, deeper gate layered on top of the pre-existing binary "any active subscription" gate on the /candidates search list itself, unchanged) and, separately, apps/deepedge/src/app/api/jobs/create/route.ts. Correction to this row's own prior text: job_post was previously described here as "deliberately left unenforced... by a prior, deliberate hybrid-gate decision (038/039)" -- that characterization does not hold up against the actual live data: company_subscriptions had zero rows platform-wide (not one company, ever, on either the old or new subscription system) while 10 of 18 real companies already had 25 real open jobs live, meaning job posting was simply never gated by anything, not upheld as a deliberate free-liquidity policy. Confirmed directly with the user before writing any code (a real monetization-launch decision, not a bug fix) rather than assuming either the old text or the opposite was correct: the answer was to enforce it, but grandfather every company that existed before this shipped onto a free 'basic' tier so none of the 10 already-posting companies are locked out, while new/future companies get the real gate from day one with no automatic grant. contact_view/job_invite/outplacement_post/placement_request remain schema-ready but genuinely unenforced -- unlike job_post, these have no corresponding feature built at all yet to consume them (outplacement today is FR-EE-13's sales-led lead-capture form, not a self-serve post), so there is nothing to wire up without building new features first, which was correctly out of scope for this pass. Sales-led Enterprise activation (FR-EE-12/13's admin Activate action) grants the unlimited Premium hiring tier automatically</v>
       </c>
       <c r="E60" t="str">
-        <v>052</v>
+        <v>096, 109</v>
       </c>
       <c r="F60" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Salt &amp; Pepper</v>
+        <v>GreyMatters</v>
       </c>
       <c r="B61" t="str">
-        <v>Community Discussions</v>
+        <v>Blogging / CMS</v>
       </c>
       <c r="C61" t="str">
-        <v>FR-SP-01</v>
+        <v>FR-GM-01</v>
       </c>
       <c r="D61" t="str">
-        <v>Members (12+ years experience gate) can start and reply to discussion threads, with anonymous posting and karma scoring</v>
+        <v>Verified authors (12+ years experience) can write, edit, and publish long-form posts with categories/tags</v>
       </c>
       <c r="E61" t="str">
-        <v>009, 025, 027</v>
+        <v>030</v>
       </c>
       <c r="F61" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Salt &amp; Pepper</v>
+        <v>GreyMatters</v>
       </c>
       <c r="B62" t="str">
-        <v>Members Directory</v>
+        <v>Blogging / CMS</v>
       </c>
       <c r="C62" t="str">
-        <v>FR-SP-02</v>
+        <v>FR-GM-02</v>
       </c>
       <c r="D62" t="str">
-        <v>A public members directory lists community members with reputation score and years of experience</v>
+        <v>Readers can comment on posts; anonymous posting is supported for sensitive topics</v>
       </c>
       <c r="E62" t="str">
-        <v>035, 047</v>
+        <v>027</v>
       </c>
       <c r="F62" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Salt &amp; Pepper</v>
+        <v>GreyMatters</v>
       </c>
       <c r="B63" t="str">
-        <v>Mentorship</v>
+        <v>Monetization</v>
       </c>
       <c r="C63" t="str">
-        <v>FR-SP-03</v>
+        <v>FR-GM-03</v>
       </c>
       <c r="D63" t="str">
-        <v>Mentor session links/availability are surfaced in discussions and member profiles</v>
+        <v>Readers can tip authors for valued posts</v>
       </c>
       <c r="E63" t="str">
-        <v>043, 056</v>
+        <v>026</v>
       </c>
       <c r="F63" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Salt &amp; Pepper</v>
+        <v>GreyMatters</v>
       </c>
       <c r="B64" t="str">
         <v>AI Quality</v>
       </c>
       <c r="C64" t="str">
-        <v>FR-SP-04</v>
+        <v>FR-GM-04</v>
       </c>
       <c r="D64" t="str">
-        <v>An LLM-based reply-quality score sweeps discussion replies on a configurable interval</v>
+        <v>An LLM-based post-quality score sweeps published posts on a configurable interval</v>
       </c>
       <c r="E64" t="str">
         <v>048, 050</v>
@@ -1694,162 +1694,162 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Salt &amp; Pepper</v>
+        <v>GreyMatters</v>
       </c>
       <c r="B65" t="str">
-        <v>Trust &amp; Safety</v>
+        <v>Newsletter</v>
       </c>
       <c r="C65" t="str">
-        <v>FR-SP-05</v>
+        <v>FR-GM-05</v>
       </c>
       <c r="D65" t="str">
-        <v>A pre-publish moderation gate blocks a genuinely-violating discussion post or reply before it is ever inserted (harassment, hate speech, spam/scams, doxxing, explicit content) -- distinct from FR-SP-04's after-the-fact quality sweep. Fails open if the LLM is unreachable/unconfigured (the post goes live rather than blocking a real user) but queues the row (moderation_status=pending_check) for automatic retry every 15 minutes; a retry that comes back BLOCK is surfaced in a new admin review queue for a human to clear or delete, never auto-removed. Emergent gap-audit item #1</v>
+        <v>Visitors can subscribe to a newsletter digest of new posts</v>
       </c>
       <c r="E65" t="str">
-        <v>098, 099</v>
+        <v>008</v>
       </c>
       <c r="F65" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Salt &amp; Pepper</v>
+        <v>GreyMatters</v>
       </c>
       <c r="B66" t="str">
-        <v>Events</v>
+        <v>Newsletter</v>
       </c>
       <c r="C66" t="str">
-        <v>FR-SP-06</v>
+        <v>FR-GM-06</v>
       </c>
       <c r="D66" t="str">
-        <v>Members can host and browse community events (title/description/time/location or virtual link/capacity), and RSVP or cancel -- a net-new feature Greyin had zero equivalent of (Emergent gap-audit item #7, code-level pass). The host is notified when someone RSVPs. Capacity is a UI-layer nicety (disables RSVP once full), not a DB-enforced ceiling</v>
+        <v>An admin can trigger a real email send (not just the in-app digest) to every newsletter subscriber, covering posts published in the last 7 days -- distinct from FR-RM-06's cross-pillar in-app digest, which deliberately skipped real email given the known SMTP rate-limit constraint; this one already sends real email at GreyMatters' own subscriber volume. Found during a full code sweep -- real, tested, never given its own FR row until now</v>
       </c>
       <c r="E66" t="str">
-        <v>100</v>
+        <v>052</v>
       </c>
       <c r="F66" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>FlexPro</v>
+        <v>Salt &amp; Pepper</v>
       </c>
       <c r="B67" t="str">
-        <v>Gig Marketplace</v>
+        <v>Community Discussions</v>
       </c>
       <c r="C67" t="str">
-        <v>FR-FA-01</v>
+        <v>FR-SP-01</v>
       </c>
       <c r="D67" t="str">
-        <v>Freelancers list gigs; clients browse/filter and place orders with Razorpay checkout</v>
+        <v>Members (12+ years experience gate) can start and reply to discussion threads, with anonymous posting and karma scoring</v>
       </c>
       <c r="E67" t="str">
-        <v>002, 029</v>
+        <v>009, 025, 027</v>
       </c>
       <c r="F67" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FlexPro</v>
+        <v>Salt &amp; Pepper</v>
       </c>
       <c r="B68" t="str">
-        <v>Order Lifecycle</v>
+        <v>Members Directory</v>
       </c>
       <c r="C68" t="str">
-        <v>FR-FA-02</v>
+        <v>FR-SP-02</v>
       </c>
       <c r="D68" t="str">
-        <v>Orders move through a lifecycle (pending → in-progress → delivered → completed) with escrow-style payment holding and webhook-driven status updates</v>
+        <v>A public members directory lists community members with reputation score and years of experience</v>
       </c>
       <c r="E68" t="str">
-        <v>002, 004, 029</v>
+        <v>035, 047</v>
       </c>
       <c r="F68" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FlexPro</v>
+        <v>Salt &amp; Pepper</v>
       </c>
       <c r="B69" t="str">
-        <v>Order Lifecycle</v>
+        <v>Mentorship</v>
       </c>
       <c r="C69" t="str">
-        <v>FR-FA-03</v>
+        <v>FR-SP-03</v>
       </c>
       <c r="D69" t="str">
-        <v>Buyer/seller can message within an order and leave a review on completion</v>
+        <v>Mentor session links/availability are surfaced in discussions and member profiles</v>
       </c>
       <c r="E69" t="str">
-        <v>005, 006</v>
+        <v>043, 056</v>
       </c>
       <c r="F69" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>FlexPro</v>
+        <v>Salt &amp; Pepper</v>
       </c>
       <c r="B70" t="str">
-        <v>Earnings &amp; Payouts</v>
+        <v>AI Quality</v>
       </c>
       <c r="C70" t="str">
-        <v>FR-FA-04</v>
+        <v>FR-SP-04</v>
       </c>
       <c r="D70" t="str">
-        <v>Freelancers can request payouts of completed-order earnings via a configurable payout rail</v>
+        <v>An LLM-based reply-quality score sweeps discussion replies on a configurable interval</v>
       </c>
       <c r="E70" t="str">
-        <v>014, 020</v>
+        <v>048, 050</v>
       </c>
       <c r="F70" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>FlexPro</v>
+        <v>Salt &amp; Pepper</v>
       </c>
       <c r="B71" t="str">
-        <v>Skill Ratings</v>
+        <v>Trust &amp; Safety</v>
       </c>
       <c r="C71" t="str">
-        <v>FR-FA-05</v>
+        <v>FR-SP-05</v>
       </c>
       <c r="D71" t="str">
-        <v>A client can rate the freelancer’s primary gig skills bidirectionally after a completed order</v>
+        <v>A pre-publish moderation gate blocks a genuinely-violating discussion post or reply before it is ever inserted (harassment, hate speech, spam/scams, doxxing, explicit content) -- distinct from FR-SP-04's after-the-fact quality sweep. Fails open if the LLM is unreachable/unconfigured (the post goes live rather than blocking a real user) but queues the row (moderation_status=pending_check) for automatic retry every 15 minutes; a retry that comes back BLOCK is surfaced in a new admin review queue for a human to clear or delete, never auto-removed. Emergent gap-audit item #1</v>
       </c>
       <c r="E71" t="str">
-        <v>054</v>
+        <v>098, 099</v>
       </c>
       <c r="F71" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>FlexPro</v>
+        <v>Salt &amp; Pepper</v>
       </c>
       <c r="B72" t="str">
-        <v>AI Quality</v>
+        <v>Events</v>
       </c>
       <c r="C72" t="str">
-        <v>FR-FA-06</v>
+        <v>FR-SP-06</v>
       </c>
       <c r="D72" t="str">
-        <v>An LLM-based delivery-quality score reviews completed order deliverables</v>
+        <v>Members can host and browse community events (title/description/time/location or virtual link/capacity), and RSVP or cancel -- a net-new feature Greyin had zero equivalent of (Emergent gap-audit item #7, code-level pass). The host is notified when someone RSVPs. Capacity is a UI-layer nicety (disables RSVP once full), not a DB-enforced ceiling</v>
       </c>
       <c r="E72" t="str">
-        <v>048</v>
+        <v>100</v>
       </c>
       <c r="F72" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="73">
@@ -1857,19 +1857,19 @@
         <v>FlexPro</v>
       </c>
       <c r="B73" t="str">
-        <v>Experience Gate</v>
+        <v>Gig Marketplace</v>
       </c>
       <c r="C73" t="str">
-        <v>FR-FA-07</v>
+        <v>FR-FA-01</v>
       </c>
       <c r="D73" t="str">
-        <v>A minimum-experience gate controls which freelancers can list gigs above a certain price tier</v>
+        <v>Freelancers list gigs; clients browse/filter and place orders with Razorpay checkout</v>
       </c>
       <c r="E73" t="str">
-        <v>039</v>
+        <v>002, 029</v>
       </c>
       <c r="F73" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="74">
@@ -1877,19 +1877,19 @@
         <v>FlexPro</v>
       </c>
       <c r="B74" t="str">
-        <v>Monetization</v>
+        <v>Order Lifecycle</v>
       </c>
       <c r="C74" t="str">
-        <v>FR-FA-08</v>
+        <v>FR-FA-02</v>
       </c>
       <c r="D74" t="str">
-        <v>A single FlexPro Pro subscription (Razorpay Subscriptions, self-serve, mirrors greyin-b2b's enterprise-subscription design) gates posting either a gig listing (as a freelancer) or a job listing (as a client). Browsing, applying to a job, and buying a gig all stay free -- only supply (posting) is gated, not demand. Replaces the "0%-commission" positioning entirely: that claim was never actually true (posting was free but the freelancer was already charged 2% at payout, the reverse of the claim) and is retired platform-wide (PILLARS description, signup/terms/gigs-new copy, pitch deck)</v>
+        <v>Orders move through a lifecycle (pending → in-progress → delivered → completed) with escrow-style payment holding and webhook-driven status updates</v>
       </c>
       <c r="E74" t="str">
-        <v>093, 094</v>
+        <v>002, 004, 029</v>
       </c>
       <c r="F74" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-10</v>
       </c>
     </row>
     <row r="75">
@@ -1897,19 +1897,19 @@
         <v>FlexPro</v>
       </c>
       <c r="B75" t="str">
-        <v>Client Jobs</v>
+        <v>Order Lifecycle</v>
       </c>
       <c r="C75" t="str">
-        <v>FR-FA-09</v>
+        <v>FR-FA-03</v>
       </c>
       <c r="D75" t="str">
-        <v>A client can post a job (title/description/budget); any member can apply for free with a proposed price; the client accepts one applicant (auto-rejecting the rest) or rejects individually. Accepting creates a real escrow order via the existing gig_orders machinery -- gig_id is nullable with client_job_application_id as the alternate origin, reusing the proven escrow/delivery/dispute/refund flow wholesale rather than duplicating it</v>
+        <v>Buyer/seller can message within an order and leave a review on completion</v>
       </c>
       <c r="E75" t="str">
-        <v>093</v>
+        <v>005, 006</v>
       </c>
       <c r="F75" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="76">
@@ -1917,19 +1917,19 @@
         <v>FlexPro</v>
       </c>
       <c r="B76" t="str">
-        <v>Monetization</v>
+        <v>Earnings &amp; Payouts</v>
       </c>
       <c r="C76" t="str">
-        <v>FR-FA-10</v>
+        <v>FR-FA-04</v>
       </c>
       <c r="D76" t="str">
-        <v>A 2% service fee applies to both sides of an accepted transaction (buyer pays amount+2%, seller nets amount-2%) -- extends the rate that was already the real gig-purchase precedent (checkout's buyer-side fee display + payouts' seller-side deduction) to the new client-job-engagement path too, rather than inventing a second number for the same concept. Stored per-order (service_fee_buyer/service_fee_seller) for audit, computed at acceptance time not at posting</v>
+        <v>Freelancers can request payouts of completed-order earnings via a configurable payout rail</v>
       </c>
       <c r="E76" t="str">
-        <v>093</v>
+        <v>014, 020</v>
       </c>
       <c r="F76" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-09</v>
       </c>
     </row>
     <row r="77">
@@ -1937,19 +1937,19 @@
         <v>FlexPro</v>
       </c>
       <c r="B77" t="str">
-        <v>Trust &amp; Safety</v>
+        <v>Skill Ratings</v>
       </c>
       <c r="C77" t="str">
-        <v>FR-FA-11</v>
+        <v>FR-FA-05</v>
       </c>
       <c r="D77" t="str">
-        <v>Either party on an order (not just the buyer, as it was) can raise a dispute for admin review -- a seller previously had no way to flag a bad-faith buyer (endless revision requests, refusal to release payment) at all. disputed_by tracks who raised it</v>
+        <v>A client can rate the freelancer’s primary gig skills bidirectionally after a completed order</v>
       </c>
       <c r="E77" t="str">
-        <v>093</v>
+        <v>054</v>
       </c>
       <c r="F77" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="78">
@@ -1957,19 +1957,19 @@
         <v>FlexPro</v>
       </c>
       <c r="B78" t="str">
-        <v>Monetization</v>
+        <v>AI Quality</v>
       </c>
       <c r="C78" t="str">
-        <v>FR-FA-12</v>
+        <v>FR-FA-06</v>
       </c>
       <c r="D78" t="str">
-        <v>The single fixed posting subscription (093) is replaced with 3 admin-priced tiers (Basic/Pro/Premium, subscription_tiers, product=freeagent_posting), each carrying a monthly gig/job-posting credit allowance (subscription_tier_credits, credit_type=gig_post, -1=unlimited) enforced atomically by consume_credit() on both api/gigs/create and api/client-jobs/create -- an active subscription alone no longer guarantees unmetered posting. /subscribe lets the user pick a tier at checkout; /admin/subscription-tiers lets an admin change any tier's price and credit allowance live</v>
+        <v>An LLM-based delivery-quality score reviews completed order deliverables</v>
       </c>
       <c r="E78" t="str">
-        <v>096</v>
+        <v>048</v>
       </c>
       <c r="F78" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="79">
@@ -1977,279 +1977,279 @@
         <v>FlexPro</v>
       </c>
       <c r="B79" t="str">
-        <v>Trust &amp; Safety</v>
+        <v>Experience Gate</v>
       </c>
       <c r="C79" t="str">
-        <v>FR-FA-13</v>
+        <v>FR-FA-07</v>
       </c>
       <c r="D79" t="str">
-        <v>A "Get AI suggestions" button on /gigs/new gives the seller 2-4 sentences of AI feedback on their draft listing (title/description clarity, missing scope, unclear pricing signals) before they publish -- stateless and on-demand (api/gigs/quality-check), informational only, never gates Publish and deliberately never calls consume_credit() so a suggestions click cannot burn a paid posting credit the way the real Publish action does (096). Emergent gap-audit item #4</v>
+        <v>A minimum-experience gate controls which freelancers can list gigs above a certain price tier</v>
       </c>
       <c r="E79" t="str">
-        <v>097</v>
+        <v>039</v>
       </c>
       <c r="F79" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>StackWorks</v>
+        <v>FlexPro</v>
       </c>
       <c r="B80" t="str">
-        <v>Projects &amp; Asks</v>
+        <v>Monetization</v>
       </c>
       <c r="C80" t="str">
-        <v>FR-SE-01</v>
+        <v>FR-FA-08</v>
       </c>
       <c r="D80" t="str">
-        <v>Builders post projects and open "asks" (roles needed); Supporters browse and apply with a pitch</v>
+        <v>A single FlexPro Pro subscription (Razorpay Subscriptions, self-serve, mirrors greyin-b2b's enterprise-subscription design) gates posting either a gig listing (as a freelancer) or a job listing (as a client). Browsing, applying to a job, and buying a gig all stay free -- only supply (posting) is gated, not demand. Replaces the "0%-commission" positioning entirely: that claim was never actually true (posting was free but the freelancer was already charged 2% at payout, the reverse of the claim) and is retired platform-wide (PILLARS description, signup/terms/gigs-new copy, pitch deck)</v>
       </c>
       <c r="E80" t="str">
-        <v>030, 047</v>
+        <v>093, 094</v>
       </c>
       <c r="F80" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>StackWorks</v>
+        <v>FlexPro</v>
       </c>
       <c r="B81" t="str">
-        <v>Application Lifecycle</v>
+        <v>Client Jobs</v>
       </c>
       <c r="C81" t="str">
-        <v>FR-SE-02</v>
+        <v>FR-FA-09</v>
       </c>
       <c r="D81" t="str">
-        <v>Builders accept/decline applications; still-pending applicants are notified if the Builder closes the ask instead</v>
+        <v>A client can post a job (title/description/budget); any member can apply for free with a proposed price; the client accepts one applicant (auto-rejecting the rest) or rejects individually. Accepting creates a real escrow order via the existing gig_orders machinery -- gig_id is nullable with client_job_application_id as the alternate origin, reusing the proven escrow/delivery/dispute/refund flow wholesale rather than duplicating it</v>
       </c>
       <c r="E81" t="str">
-        <v>030, 051</v>
+        <v>093</v>
       </c>
       <c r="F81" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>StackWorks</v>
+        <v>FlexPro</v>
       </c>
       <c r="B82" t="str">
-        <v>Verification</v>
+        <v>Monetization</v>
       </c>
       <c r="C82" t="str">
-        <v>FR-SE-03</v>
+        <v>FR-FA-10</v>
       </c>
       <c r="D82" t="str">
-        <v>Supporters submit work against verification criteria; an LLM reviews it for an AI score, and the Builder finalizes with a human score. A Builder can also self-submit a project_shipped outcome for their own project (no application_id) -- gated so the subject can never be their own reviewer (033), only an admin can</v>
+        <v>A 2% service fee applies to both sides of an accepted transaction (buyer pays amount+2%, seller nets amount-2%) -- extends the rate that was already the real gig-purchase precedent (checkout's buyer-side fee display + payouts' seller-side deduction) to the new client-job-engagement path too, rather than inventing a second number for the same concept. Stored per-order (service_fee_buyer/service_fee_seller) for audit, computed at acceptance time not at posting</v>
       </c>
       <c r="E82" t="str">
-        <v>031, 032, 033, 034, 048</v>
+        <v>093</v>
       </c>
       <c r="F82" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>StackWorks</v>
+        <v>FlexPro</v>
       </c>
       <c r="B83" t="str">
-        <v>Track Record</v>
+        <v>Trust &amp; Safety</v>
       </c>
       <c r="C83" t="str">
-        <v>FR-SE-04</v>
+        <v>FR-FA-11</v>
       </c>
       <c r="D83" t="str">
-        <v>Verified outcomes accumulate into a public, per-user track record (count + average score)</v>
+        <v>Either party on an order (not just the buyer, as it was) can raise a dispute for admin review -- a seller previously had no way to flag a bad-faith buyer (endless revision requests, refusal to release payment) at all. disputed_by tracks who raised it</v>
       </c>
       <c r="E83" t="str">
-        <v>031</v>
+        <v>093</v>
       </c>
       <c r="F83" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>StackWorks</v>
+        <v>FlexPro</v>
       </c>
       <c r="B84" t="str">
-        <v>People Directory</v>
+        <v>Monetization</v>
       </c>
       <c r="C84" t="str">
-        <v>FR-SE-05</v>
+        <v>FR-FA-12</v>
       </c>
       <c r="D84" t="str">
-        <v>A public People directory lists Builders/Supporters with role pill, Greyin Score, and track record</v>
+        <v>The single fixed posting subscription (093) is replaced with 3 admin-priced tiers (Basic/Pro/Premium, subscription_tiers, product=freeagent_posting), each carrying a monthly gig/job-posting credit allowance (subscription_tier_credits, credit_type=gig_post, -1=unlimited) enforced atomically by consume_credit() on both api/gigs/create and api/client-jobs/create -- an active subscription alone no longer guarantees unmetered posting. /subscribe lets the user pick a tier at checkout; /admin/subscription-tiers lets an admin change any tier's price and credit allowance live</v>
       </c>
       <c r="E84" t="str">
-        <v>035, 036, 047</v>
+        <v>096</v>
       </c>
       <c r="F84" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>StackWorks</v>
+        <v>FlexPro</v>
       </c>
       <c r="B85" t="str">
-        <v>Skill Ratings</v>
+        <v>Trust &amp; Safety</v>
       </c>
       <c r="C85" t="str">
-        <v>FR-SE-06</v>
+        <v>FR-FA-13</v>
       </c>
       <c r="D85" t="str">
-        <v>Builder/Supporter can bidirectionally rate each other’s skills after a gated interaction (chat/application-accepted, revisable after verified outcome)</v>
+        <v>A "Get AI suggestions" button on /gigs/new gives the seller 2-4 sentences of AI feedback on their draft listing (title/description clarity, missing scope, unclear pricing signals) before they publish -- stateless and on-demand (api/gigs/quality-check), informational only, never gates Publish and deliberately never calls consume_credit() so a suggestions click cannot burn a paid posting credit the way the real Publish action does (096). Emergent gap-audit item #4</v>
       </c>
       <c r="E85" t="str">
-        <v>054</v>
+        <v>097</v>
       </c>
       <c r="F85" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Platform-Wide</v>
+        <v>StackWorks</v>
       </c>
       <c r="B86" t="str">
-        <v>Admin: LLM</v>
+        <v>Projects &amp; Asks</v>
       </c>
       <c r="C86" t="str">
-        <v>FR-SE-07</v>
+        <v>FR-SE-01</v>
       </c>
       <c r="D86" t="str">
-        <v>Admins can add/disable/delete LLM provider rows and toggle feature flags, including per-flag sweep intervals — moved from StackWorks to Greyin Hub's /admin/llm 2026-08-24 (see FR-PW-15)</v>
+        <v>Builders post projects and open "asks" (roles needed); Supporters browse and apply with a pitch</v>
       </c>
       <c r="E86" t="str">
-        <v>048, 050</v>
+        <v>030, 047</v>
       </c>
       <c r="F86" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Roadmap (Audit)</v>
+        <v>StackWorks</v>
       </c>
       <c r="B87" t="str">
-        <v>Mentorship</v>
+        <v>Application Lifecycle</v>
       </c>
       <c r="C87" t="str">
-        <v>FR-RM-01</v>
+        <v>FR-SE-02</v>
       </c>
       <c r="D87" t="str">
-        <v>Mentors can run cohort/group sessions (capacity &gt; 1), sell bulk session packages redeemable as credits, and sell paid access to a past session's recording</v>
+        <v>Builders accept/decline applications; still-pending applicants are notified if the Builder closes the ask instead</v>
       </c>
       <c r="E87" t="str">
-        <v>062</v>
+        <v>030, 051</v>
       </c>
       <c r="F87" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Roadmap (Audit)</v>
+        <v>StackWorks</v>
       </c>
       <c r="B88" t="str">
-        <v>StackWorks Portfolio</v>
+        <v>Verification</v>
       </c>
       <c r="C88" t="str">
-        <v>FR-RM-02</v>
+        <v>FR-SE-03</v>
       </c>
       <c r="D88" t="str">
-        <v>A public, unauthenticated SVG badge shows a user's verified-outcome count and Greyin Score, embeddable outside the app (resume, LinkedIn)</v>
+        <v>Supporters submit work against verification criteria; an LLM reviews it for an AI score, and the Builder finalizes with a human score. A Builder can also self-submit a project_shipped outcome for their own project (no application_id) -- gated so the subject can never be their own reviewer (033), only an admin can</v>
       </c>
       <c r="E88" t="str">
-        <v>060 (no new schema)</v>
+        <v>031, 032, 033, 034, 048</v>
       </c>
       <c r="F88" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Roadmap (Audit)</v>
+        <v>StackWorks</v>
       </c>
       <c r="B89" t="str">
-        <v>FlexPro Trust</v>
+        <v>Track Record</v>
       </c>
       <c r="C89" t="str">
-        <v>FR-RM-03</v>
+        <v>FR-SE-04</v>
       </c>
       <c r="D89" t="str">
-        <v>A "Top Tier" badge auto-computed from an existing Verified Expert + high FlexPro-specific Greyin Score threshold surfaces on gig and seller pages</v>
+        <v>Verified outcomes accumulate into a public, per-user track record (count + average score)</v>
       </c>
       <c r="E89" t="str">
-        <v>036 (no new schema, auto-threshold read)</v>
+        <v>031</v>
       </c>
       <c r="F89" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-15</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Roadmap (Audit)</v>
+        <v>StackWorks</v>
       </c>
       <c r="B90" t="str">
-        <v>GreyMatters Reach</v>
+        <v>People Directory</v>
       </c>
       <c r="C90" t="str">
-        <v>FR-RM-04</v>
+        <v>FR-SE-05</v>
       </c>
       <c r="D90" t="str">
-        <v>A candidate's published GreyMatters articles surface directly on their open DeepEdge profile</v>
+        <v>A public People directory lists Builders/Supporters with role pill, Greyin Score, and track record</v>
       </c>
       <c r="E90" t="str">
-        <v>none (shared-schema cross-app read)</v>
+        <v>035, 036, 047</v>
       </c>
       <c r="F90" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Roadmap (Audit)</v>
+        <v>StackWorks</v>
       </c>
       <c r="B91" t="str">
-        <v>DeepEdge SEO</v>
+        <v>Skill Ratings</v>
       </c>
       <c r="C91" t="str">
-        <v>FR-RM-05</v>
+        <v>FR-SE-06</v>
       </c>
       <c r="D91" t="str">
-        <v>Open jobs and companies are listed in a sitemap.xml, and job detail pages carry schema.org JobPosting JSON-LD structured data</v>
+        <v>Builder/Supporter can bidirectionally rate each other’s skills after a gated interaction (chat/application-accepted, revisable after verified outcome)</v>
       </c>
       <c r="E91" t="str">
-        <v>none (app-layer only)</v>
+        <v>054</v>
       </c>
       <c r="F91" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Roadmap (Audit)</v>
+        <v>Platform-Wide</v>
       </c>
       <c r="B92" t="str">
-        <v>Retention</v>
+        <v>Admin: LLM</v>
       </c>
       <c r="C92" t="str">
-        <v>FR-RM-06</v>
+        <v>FR-SE-07</v>
       </c>
       <c r="D92" t="str">
-        <v>An in-app "this week across Greyin" digest summarizes the last 7 days of cross-pillar notifications on the dashboard, in place of a real email send</v>
+        <v>Admins can add/disable/delete LLM provider rows and toggle feature flags, including per-flag sweep intervals — moved from StackWorks to Greyin Hub's /admin/llm 2026-08-24 (see FR-PW-15)</v>
       </c>
       <c r="E92" t="str">
-        <v>none (reads existing notifications table)</v>
+        <v>048, 050</v>
       </c>
       <c r="F92" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="93">
@@ -2257,16 +2257,16 @@
         <v>Roadmap (Audit)</v>
       </c>
       <c r="B93" t="str">
-        <v>Retention</v>
+        <v>Mentorship</v>
       </c>
       <c r="C93" t="str">
-        <v>FR-RM-07</v>
+        <v>FR-RM-01</v>
       </c>
       <c r="D93" t="str">
-        <v>Users can watch a (role, level, location) salary trend and get notified when it moves &gt;=15% since they last checked</v>
+        <v>Mentors can run cohort/group sessions (capacity &gt; 1), sell bulk session packages redeemable as credits, and sell paid access to a past session's recording</v>
       </c>
       <c r="E93" t="str">
-        <v>063</v>
+        <v>062</v>
       </c>
       <c r="F93" t="str">
         <v>2026-08-23</v>
@@ -2277,16 +2277,16 @@
         <v>Roadmap (Audit)</v>
       </c>
       <c r="B94" t="str">
-        <v>DeepEdge Salary Data</v>
+        <v>StackWorks Portfolio</v>
       </c>
       <c r="C94" t="str">
-        <v>FR-RM-08</v>
+        <v>FR-RM-02</v>
       </c>
       <c r="D94" t="str">
-        <v>Employers can mark a job's salary range as publicly disclosed when posting or editing it, feeding the k-anonymized salary_trends view's market source (previously never wired up despite the UI fields existing)</v>
+        <v>A public, unauthenticated SVG badge shows a user's verified-outcome count and Greyin Score, embeddable outside the app (resume, LinkedIn)</v>
       </c>
       <c r="E94" t="str">
-        <v>none (app-layer fix)</v>
+        <v>060 (no new schema)</v>
       </c>
       <c r="F94" t="str">
         <v>2026-08-23</v>
@@ -2294,107 +2294,227 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Longlist</v>
+        <v>Roadmap (Audit)</v>
       </c>
       <c r="B95" t="str">
-        <v>Future Roles</v>
+        <v>FlexPro Trust</v>
       </c>
       <c r="C95" t="str">
-        <v>FR-LL-01</v>
+        <v>FR-RM-03</v>
       </c>
       <c r="D95" t="str">
-        <v>Companies post roles they expect to open 3/6/9/12 months out; the company's identity is withheld from every browsing member via a hand-curated, column-filtered view (future_roles_public), not app-layer filtering of the base table</v>
+        <v>A "Top Tier" badge auto-computed from an existing Verified Expert + high FlexPro-specific Greyin Score threshold surfaces on gig and seller pages</v>
       </c>
       <c r="E95" t="str">
-        <v>087</v>
+        <v>036 (no new schema, auto-threshold read)</v>
       </c>
       <c r="F95" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Longlist</v>
+        <v>Roadmap (Audit)</v>
       </c>
       <c r="B96" t="str">
-        <v>Future Roles</v>
+        <v>GreyMatters Reach</v>
       </c>
       <c r="C96" t="str">
-        <v>FR-LL-02</v>
+        <v>FR-RM-04</v>
       </c>
       <c r="D96" t="str">
-        <v>A member can subscribe to a future role as "future-interested" with one click (not an application); doing so makes their profile visible to that role's poster, and nothing else changes</v>
+        <v>A candidate's published GreyMatters articles surface directly on their open DeepEdge profile</v>
       </c>
       <c r="E96" t="str">
-        <v>087, 088</v>
+        <v>none (shared-schema cross-app read)</v>
       </c>
       <c r="F96" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Longlist</v>
+        <v>Roadmap (Audit)</v>
       </c>
       <c r="B97" t="str">
-        <v>Future Interests</v>
+        <v>DeepEdge SEO</v>
       </c>
       <c r="C97" t="str">
-        <v>FR-LL-03</v>
+        <v>FR-RM-05</v>
       </c>
       <c r="D97" t="str">
-        <v>A member can optionally state future career interests (skills + free text) on their profile, independent of any specific role, as a standing signal for AI matching</v>
+        <v>Open jobs and companies are listed in a sitemap.xml, and job detail pages carry schema.org JobPosting JSON-LD structured data</v>
       </c>
       <c r="E97" t="str">
-        <v>087</v>
+        <v>none (app-layer only)</v>
       </c>
       <c r="F97" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Longlist</v>
+        <v>Roadmap (Audit)</v>
       </c>
       <c r="B98" t="str">
-        <v>AI Matching</v>
+        <v>Retention</v>
       </c>
       <c r="C98" t="str">
-        <v>FR-LL-04</v>
+        <v>FR-RM-06</v>
       </c>
       <c r="D98" t="str">
-        <v>A second, AI-surfaced candidate list (distinct from explicit subscribers) is shown to a role's poster, ranking platform members against the role by stated future interests -- gated by the shared llm_feature_flags registry, off by default given it surfaces profiles to an employer with no explicit opt-in for that specific role</v>
+        <v>An in-app "this week across Greyin" digest summarizes the last 7 days of cross-pillar notifications on the dashboard, in place of a real email send</v>
       </c>
       <c r="E98" t="str">
-        <v>087</v>
+        <v>none (reads existing notifications table)</v>
       </c>
       <c r="F98" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>Roadmap (Audit)</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Retention</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FR-RM-07</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Users can watch a (role, level, location) salary trend and get notified when it moves &gt;=15% since they last checked</v>
+      </c>
+      <c r="E99" t="str">
+        <v>063</v>
+      </c>
+      <c r="F99" t="str">
+        <v>2026-08-23</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Roadmap (Audit)</v>
+      </c>
+      <c r="B100" t="str">
+        <v>DeepEdge Salary Data</v>
+      </c>
+      <c r="C100" t="str">
+        <v>FR-RM-08</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Employers can mark a job's salary range as publicly disclosed when posting or editing it, feeding the k-anonymized salary_trends view's market source (previously never wired up despite the UI fields existing)</v>
+      </c>
+      <c r="E100" t="str">
+        <v>none (app-layer fix)</v>
+      </c>
+      <c r="F100" t="str">
+        <v>2026-08-23</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>Longlist</v>
       </c>
-      <c r="B99" t="str">
+      <c r="B101" t="str">
+        <v>Future Roles</v>
+      </c>
+      <c r="C101" t="str">
+        <v>FR-LL-01</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Companies post roles they expect to open 3/6/9/12 months out; the company's identity is withheld from every browsing member via a hand-curated, column-filtered view (future_roles_public), not app-layer filtering of the base table</v>
+      </c>
+      <c r="E101" t="str">
+        <v>087</v>
+      </c>
+      <c r="F101" t="str">
+        <v>2026-09-01</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Longlist</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Future Roles</v>
+      </c>
+      <c r="C102" t="str">
+        <v>FR-LL-02</v>
+      </c>
+      <c r="D102" t="str">
+        <v>A member can subscribe to a future role as "future-interested" with one click (not an application); doing so makes their profile visible to that role's poster, and nothing else changes</v>
+      </c>
+      <c r="E102" t="str">
+        <v>087, 088</v>
+      </c>
+      <c r="F102" t="str">
+        <v>2026-09-01</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Longlist</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Future Interests</v>
+      </c>
+      <c r="C103" t="str">
+        <v>FR-LL-03</v>
+      </c>
+      <c r="D103" t="str">
+        <v>A member can optionally state future career interests (skills + free text) on their profile, independent of any specific role, as a standing signal for AI matching</v>
+      </c>
+      <c r="E103" t="str">
+        <v>087</v>
+      </c>
+      <c r="F103" t="str">
+        <v>2026-09-01</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Longlist</v>
+      </c>
+      <c r="B104" t="str">
+        <v>AI Matching</v>
+      </c>
+      <c r="C104" t="str">
+        <v>FR-LL-04</v>
+      </c>
+      <c r="D104" t="str">
+        <v>A second, AI-surfaced candidate list (distinct from explicit subscribers) is shown to a role's poster, ranking platform members against the role by stated future interests -- gated by the shared llm_feature_flags registry, off by default given it surfaces profiles to an employer with no explicit opt-in for that specific role. Real, significant bug found and fixed while adding e2e coverage (2026-09-04, direct user request): this had been completely non-functional since it shipped, for every user, regardless of the feature flag -- 087 correctly added future_interests/future_interests_note to platform_people_index, but 103_flexpro_rename.sql later redefined the same view from a stale pre-087 base copy (renaming an unrelated pillar-score column elsewhere in it) and silently dropped both columns via CREATE OR REPLACE VIEW; 105_stackworks_rename.sql then explicitly carried "103's exact body, unchanged" forward, repeating the same regression. A PostgREST query selecting a column the view doesn't have errors out entirely, so match-candidates.ts's own people fetch always came back null and hit its `if (!people...) return []` guard before ever calling the LLM -- indistinguishable in the UI from the flag being off or no profile fitting, which is exactly why it went unnoticed this long. Fixed in 111_restore_future_interests_on_people_index.sql (the view's current full column set plus the two 087 columns, nothing else changed) plus a supabase_rest force-restart for the same PostgREST-schema-cache-staleness class this deployment has hit before (NFR-OPS-01). Verified end to end against real prod, not just the query: a real member states a future interest, a real employer posts a matching role with the flag freshly enabled, and the real (non-deterministic) LLM call surfaces that member by name with a reason -- confirmed failing before the fix (empty AI-surfaced list) and passing after it, isolating the fix as the actual cause rather than assuming</v>
+      </c>
+      <c r="E104" t="str">
+        <v>087, 111</v>
+      </c>
+      <c r="F104" t="str">
+        <v>2026-08-23</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Longlist</v>
+      </c>
+      <c r="B105" t="str">
         <v>Role Lifecycle</v>
       </c>
-      <c r="C99" t="str">
+      <c r="C105" t="str">
         <v>FR-LL-05</v>
       </c>
-      <c r="D99" t="str">
-        <v>A role's poster can mark it filled or expired; every subscriber is notified when a role they were interested in closes</v>
-      </c>
-      <c r="E99" t="str">
-        <v>087</v>
-      </c>
-      <c r="F99" t="str">
-        <v>2026-09-01</v>
+      <c r="D105" t="str">
+        <v>A role's poster can mark it filled or expired; every subscriber is notified when a role they were interested in closes. Two real gaps found and fixed while adding e2e coverage (2026-09-04, direct user request): (1) the notify_future_role_filled() trigger 087 shipped only ever checked `NEW.status = 'filled'`, never 'expired', despite this row's own stated intent explicitly covering both ("every subscriber is notified when a role...closes") -- a subscriber to a role that quietly expired was never notified at all, fixed in 110_fix_future_role_expired_notification.sql; (2) 'expired' was already a real, API-accepted (see VALID_STATUSES in the status route), notification-wired status, but apps/longlist/src/app/employer/roles/page.tsx only ever rendered a "Mark filled" button -- there was no way for a real poster to reach 'expired' at all, fixed by adding a "Mark expired" button identical in shape to the existing one. Verified end to end against real prod: two roles posted, one subscriber each, one role marked filled and the other marked expired through the real UI, both subscribers confirmed to receive the real notification</v>
+      </c>
+      <c r="E105" t="str">
+        <v>087, 110</v>
+      </c>
+      <c r="F105" t="str">
+        <v>2026-08-23</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F105"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2810,7 +2930,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H105"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -3812,623 +3932,623 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FR-EE-01</v>
+        <v>FR-PW-38</v>
       </c>
       <c r="B39" t="str">
-        <v>Post/browse/apply to jobs</v>
+        <v>Admin dashboard card on the Hub, linking to /admin, role-gated</v>
       </c>
       <c r="C39" t="str">
         <v>Y</v>
       </c>
       <c r="D39" t="str">
-        <v>001, 003</v>
+        <v>none</v>
       </c>
       <c r="E39" t="str">
         <v>Y</v>
       </c>
       <c r="F39" t="str">
-        <v>jobs-and-applications.spec.ts, jobs-filters.spec.ts, job-edit.spec.ts</v>
+        <v>admin-dashboard-link.spec.ts</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-21 / 2026-08-23</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>FR-EE-02</v>
+        <v>FR-PW-39</v>
       </c>
       <c r="B40" t="str">
-        <v>Application status review</v>
+        <v>Longlist activity coverage in my_pillar_activity + DeepEdge pillar-color rename fix</v>
       </c>
       <c r="C40" t="str">
         <v>Y</v>
       </c>
       <c r="D40" t="str">
-        <v>001, 017</v>
+        <v>108</v>
       </c>
       <c r="E40" t="str">
         <v>Y</v>
       </c>
       <c r="F40" t="str">
-        <v>jobs-and-applications.spec.ts</v>
+        <v>longlist-activity.spec.ts</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-23</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>FR-EE-03</v>
+        <v>FR-PW-40</v>
       </c>
       <c r="B41" t="str">
-        <v>Public company directory</v>
+        <v>Light/dark mode foundation (toggle, persistence, FOUC-free init) on all 7 apps; shared chrome + homepage styled; inner pages completed same-day in FR-PW-41</v>
       </c>
       <c r="C41" t="str">
         <v>Y</v>
       </c>
       <c r="D41" t="str">
-        <v>001</v>
+        <v>none</v>
       </c>
       <c r="E41" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F41" t="str">
-        <v>companies.spec.ts</v>
+        <v>manual Playwright verification against prod; no permanent e2e spec yet</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-11</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>FR-EE-04</v>
+        <v>FR-PW-41</v>
       </c>
       <c r="B42" t="str">
-        <v>Eligibility-gated company reviews</v>
+        <v>Dark-mode styling on all 169 pages across 7 apps + ThemeToggle added to 73/89 inline-header pages lacking the shared SiteHeader</v>
       </c>
       <c r="C42" t="str">
         <v>Y</v>
       </c>
       <c r="D42" t="str">
-        <v>058</v>
+        <v>none</v>
       </c>
       <c r="E42" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F42" t="str">
-        <v>company-reviews.spec.ts</v>
+        <v>manual Playwright verification against prod; no permanent e2e spec yet</v>
       </c>
       <c r="G42" t="str">
         <v>2026-08-23</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-23</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>FR-EE-05</v>
+        <v>FR-PW-42</v>
       </c>
       <c r="B43" t="str">
-        <v>Anonymous company review display</v>
+        <v>ThemeToggle added to the remaining 16 inline-header pages, closing FR-PW-41's gap -- 89/89 (100%) coverage</v>
       </c>
       <c r="C43" t="str">
         <v>Y</v>
       </c>
       <c r="D43" t="str">
-        <v>058</v>
+        <v>none</v>
       </c>
       <c r="E43" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F43" t="str">
-        <v>company-reviews.spec.ts</v>
+        <v>manual Playwright verification (3 pages) + typecheck/build/source verification (4 auth-gated pages); no permanent e2e spec yet</v>
       </c>
       <c r="G43" t="str">
         <v>2026-08-23</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-23</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FR-EE-06</v>
+        <v>FR-PW-43</v>
       </c>
       <c r="B44" t="str">
-        <v>Resume parse + structured employment history</v>
+        <v>Permanent dark-mode e2e test + rss.xml crash fix + gradient-background dark:variant fix on all 40 auth/browse pages missed by FR-PW-41</v>
       </c>
       <c r="C44" t="str">
         <v>Y</v>
       </c>
       <c r="D44" t="str">
-        <v>029, 055</v>
+        <v>none</v>
       </c>
       <c r="E44" t="str">
         <v>Y</v>
       </c>
       <c r="F44" t="str">
-        <v>resume-parsing.spec.ts, employment-history.spec.ts</v>
+        <v>dark-mode-toggle.spec.ts (all 7 domains)</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-11 / 2026-08-22</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>FR-EE-07</v>
+        <v>FR-EE-01</v>
       </c>
       <c r="B45" t="str">
-        <v>Paywalled candidate search / open profile</v>
+        <v>Post/browse/apply to jobs</v>
       </c>
       <c r="C45" t="str">
         <v>Y</v>
       </c>
       <c r="D45" t="str">
-        <v>039</v>
+        <v>001, 003</v>
       </c>
       <c r="E45" t="str">
         <v>Y</v>
       </c>
       <c r="F45" t="str">
-        <v>subscription-gate.spec.ts, candidates.spec.ts</v>
+        <v>jobs-and-applications.spec.ts, jobs-filters.spec.ts, job-edit.spec.ts</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-06</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-21 / 2026-08-23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>FR-EE-08</v>
+        <v>FR-EE-02</v>
       </c>
       <c r="B46" t="str">
-        <v>Razorpay employer subscriptions</v>
+        <v>Application status review</v>
       </c>
       <c r="C46" t="str">
         <v>Y</v>
       </c>
       <c r="D46" t="str">
-        <v>002, 039</v>
+        <v>001, 017</v>
       </c>
       <c r="E46" t="str">
         <v>Y</v>
       </c>
       <c r="F46" t="str">
-        <v>subscription-gate.spec.ts</v>
+        <v>jobs-and-applications.spec.ts</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-09</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>FR-EE-09</v>
+        <v>FR-EE-03</v>
       </c>
       <c r="B47" t="str">
-        <v>Enterprise solutions intake</v>
+        <v>Public company directory</v>
       </c>
       <c r="C47" t="str">
         <v>Y</v>
       </c>
       <c r="D47" t="str">
-        <v>044</v>
+        <v>001</v>
       </c>
       <c r="E47" t="str">
         <v>Y</v>
       </c>
       <c r="F47" t="str">
-        <v>enterprise-solutions.spec.ts</v>
+        <v>companies.spec.ts</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-06</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>FR-EE-10</v>
+        <v>FR-EE-04</v>
       </c>
       <c r="B48" t="str">
-        <v>Gate-threshold governance voting</v>
+        <v>Eligibility-gated company reviews</v>
       </c>
       <c r="C48" t="str">
         <v>Y</v>
       </c>
       <c r="D48" t="str">
-        <v>041</v>
+        <v>058</v>
       </c>
       <c r="E48" t="str">
         <v>Y</v>
       </c>
       <c r="F48" t="str">
-        <v>governance-voting.spec.ts</v>
+        <v>company-reviews.spec.ts</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>FR-EE-11</v>
+        <v>FR-EE-05</v>
       </c>
       <c r="B49" t="str">
-        <v>Job alerts</v>
+        <v>Anonymous company review display</v>
       </c>
       <c r="C49" t="str">
         <v>Y</v>
       </c>
       <c r="D49" t="str">
-        <v>023</v>
+        <v>058</v>
       </c>
       <c r="E49" t="str">
         <v>Y</v>
       </c>
       <c r="F49" t="str">
-        <v>job-alerts.spec.ts</v>
+        <v>company-reviews.spec.ts</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>FR-EE-12</v>
+        <v>FR-EE-06</v>
       </c>
       <c r="B50" t="str">
-        <v>Fractional leadership lead capture + admin triage</v>
+        <v>Resume parse + structured employment history</v>
       </c>
       <c r="C50" t="str">
         <v>Y</v>
       </c>
       <c r="D50" t="str">
-        <v>039, 044</v>
+        <v>029, 055</v>
       </c>
       <c r="E50" t="str">
         <v>Y</v>
       </c>
       <c r="F50" t="str">
-        <v>enterprise-solutions.spec.ts</v>
+        <v>resume-parsing.spec.ts, employment-history.spec.ts</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-22</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-11 / 2026-08-22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>FR-EE-13</v>
+        <v>FR-EE-07</v>
       </c>
       <c r="B51" t="str">
-        <v>Outplacement lead capture + admin triage</v>
+        <v>Paywalled candidate search / open profile</v>
       </c>
       <c r="C51" t="str">
         <v>Y</v>
       </c>
       <c r="D51" t="str">
-        <v>039, 044</v>
+        <v>039</v>
       </c>
       <c r="E51" t="str">
         <v>Y</v>
       </c>
       <c r="F51" t="str">
-        <v>enterprise-solutions.spec.ts</v>
+        <v>subscription-gate.spec.ts, candidates.spec.ts</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-17</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>FR-EE-14</v>
+        <v>FR-EE-08</v>
       </c>
       <c r="B52" t="str">
-        <v>Candidate application withdrawal</v>
+        <v>Razorpay employer subscriptions</v>
       </c>
       <c r="C52" t="str">
         <v>Y</v>
       </c>
       <c r="D52" t="str">
-        <v>092</v>
+        <v>002, 039</v>
       </c>
       <c r="E52" t="str">
         <v>Y</v>
       </c>
       <c r="F52" t="str">
-        <v>application-withdrawal.spec.ts</v>
+        <v>subscription-gate.spec.ts</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-17</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>FR-EE-15</v>
+        <v>FR-EE-09</v>
       </c>
       <c r="B53" t="str">
-        <v>Employer self-service job close/reopen</v>
+        <v>Enterprise solutions intake</v>
       </c>
       <c r="C53" t="str">
         <v>Y</v>
       </c>
       <c r="D53" t="str">
-        <v>092</v>
+        <v>044</v>
       </c>
       <c r="E53" t="str">
         <v>Y</v>
       </c>
       <c r="F53" t="str">
-        <v>job-close-reopen.spec.ts</v>
+        <v>enterprise-solutions.spec.ts</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-18</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>FR-EE-16</v>
+        <v>FR-EE-10</v>
       </c>
       <c r="B54" t="str">
-        <v>3-tier hiring subscription + admin-configurable credits (profile_view enforced; job_post/contact_view/job_invite/outplacement_post/placement_request schema-ready, not yet enforced)</v>
+        <v>Gate-threshold governance voting</v>
       </c>
       <c r="C54" t="str">
         <v>Y</v>
       </c>
       <c r="D54" t="str">
-        <v>096</v>
+        <v>041</v>
       </c>
       <c r="E54" t="str">
         <v>Y</v>
       </c>
       <c r="F54" t="str">
-        <v>candidate-profile-credits.spec.ts</v>
+        <v>governance-voting.spec.ts</v>
       </c>
       <c r="G54" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-18</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>FR-GM-01</v>
+        <v>FR-EE-11</v>
       </c>
       <c r="B55" t="str">
-        <v>Author CMS (post/edit/publish)</v>
+        <v>Job alerts</v>
       </c>
       <c r="C55" t="str">
         <v>Y</v>
       </c>
       <c r="D55" t="str">
-        <v>030</v>
+        <v>023</v>
       </c>
       <c r="E55" t="str">
         <v>Y</v>
       </c>
       <c r="F55" t="str">
-        <v>post-cms.spec.ts</v>
+        <v>job-alerts.spec.ts</v>
       </c>
       <c r="G55" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-09</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-11</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>FR-GM-02</v>
+        <v>FR-EE-12</v>
       </c>
       <c r="B56" t="str">
-        <v>Comments + anonymous posting</v>
+        <v>Fractional leadership lead capture + admin triage</v>
       </c>
       <c r="C56" t="str">
         <v>Y</v>
       </c>
       <c r="D56" t="str">
-        <v>027</v>
+        <v>039, 044</v>
       </c>
       <c r="E56" t="str">
         <v>Y</v>
       </c>
       <c r="F56" t="str">
-        <v>comments-and-categories.spec.ts</v>
+        <v>enterprise-solutions.spec.ts</v>
       </c>
       <c r="G56" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-18</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-11</v>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>FR-GM-03</v>
+        <v>FR-EE-13</v>
       </c>
       <c r="B57" t="str">
-        <v>Author tips</v>
+        <v>Outplacement lead capture + admin triage</v>
       </c>
       <c r="C57" t="str">
         <v>Y</v>
       </c>
       <c r="D57" t="str">
-        <v>026</v>
+        <v>039, 044</v>
       </c>
       <c r="E57" t="str">
         <v>Y</v>
       </c>
       <c r="F57" t="str">
-        <v>tips.spec.ts</v>
+        <v>enterprise-solutions.spec.ts</v>
       </c>
       <c r="G57" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-18</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-12</v>
+        <v>2026-08-18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>FR-GM-04</v>
+        <v>FR-EE-14</v>
       </c>
       <c r="B58" t="str">
-        <v>AI post-quality sweep</v>
+        <v>Candidate application withdrawal</v>
       </c>
       <c r="C58" t="str">
         <v>Y</v>
       </c>
       <c r="D58" t="str">
-        <v>048, 050</v>
+        <v>092</v>
       </c>
       <c r="E58" t="str">
         <v>Y</v>
       </c>
       <c r="F58" t="str">
-        <v>ai-quality-score.spec.ts, admin-sweep.spec.ts, admin-digest-send.spec.ts</v>
+        <v>application-withdrawal.spec.ts</v>
       </c>
       <c r="G58" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-21</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>FR-GM-05</v>
+        <v>FR-EE-15</v>
       </c>
       <c r="B59" t="str">
-        <v>Newsletter subscribe</v>
+        <v>Employer self-service job close/reopen</v>
       </c>
       <c r="C59" t="str">
         <v>Y</v>
       </c>
       <c r="D59" t="str">
-        <v>008</v>
+        <v>092</v>
       </c>
       <c r="E59" t="str">
         <v>Y</v>
       </c>
       <c r="F59" t="str">
-        <v>newsletter-and-search.spec.ts</v>
+        <v>job-close-reopen.spec.ts</v>
       </c>
       <c r="G59" t="str">
-        <v>2026-08-07</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-15</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>FR-GM-06</v>
+        <v>FR-EE-16</v>
       </c>
       <c r="B60" t="str">
-        <v>Admin-triggered newsletter digest email send</v>
+        <v>3-tier hiring subscription + admin-configurable credits (profile_view + job_post now enforced, 109 grandfathers pre-existing companies; contact_view/job_invite/outplacement_post/placement_request schema-ready, no consuming feature built yet)</v>
       </c>
       <c r="C60" t="str">
         <v>Y</v>
       </c>
       <c r="D60" t="str">
-        <v>052</v>
+        <v>096, 109</v>
       </c>
       <c r="E60" t="str">
         <v>Y</v>
       </c>
       <c r="F60" t="str">
-        <v>admin-digest-send.spec.ts</v>
+        <v>candidate-profile-credits.spec.ts, job-post-credits.spec.ts</v>
       </c>
       <c r="G60" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-21</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>FR-SP-01</v>
+        <v>FR-GM-01</v>
       </c>
       <c r="B61" t="str">
-        <v>Discussions + karma + anonymous posting</v>
+        <v>Author CMS (post/edit/publish)</v>
       </c>
       <c r="C61" t="str">
         <v>Y</v>
       </c>
       <c r="D61" t="str">
-        <v>009, 025, 027</v>
+        <v>030</v>
       </c>
       <c r="E61" t="str">
         <v>Y</v>
       </c>
       <c r="F61" t="str">
-        <v>discussions.spec.ts, karma-and-anonymous.spec.ts</v>
+        <v>post-cms.spec.ts</v>
       </c>
       <c r="G61" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-14</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-11 / 2026-08-12</v>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>FR-SP-02</v>
+        <v>FR-GM-02</v>
       </c>
       <c r="B62" t="str">
-        <v>Public members directory</v>
+        <v>Comments + anonymous posting</v>
       </c>
       <c r="C62" t="str">
         <v>Y</v>
       </c>
       <c r="D62" t="str">
-        <v>035, 047</v>
+        <v>027</v>
       </c>
       <c r="E62" t="str">
         <v>Y</v>
       </c>
       <c r="F62" t="str">
-        <v>members.spec.ts</v>
+        <v>comments-and-categories.spec.ts</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-09</v>
       </c>
       <c r="H62" t="str">
         <v>2026-08-11</v>
@@ -4436,36 +4556,36 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>FR-SP-03</v>
+        <v>FR-GM-03</v>
       </c>
       <c r="B63" t="str">
-        <v>Mentor session links in community</v>
+        <v>Author tips</v>
       </c>
       <c r="C63" t="str">
         <v>Y</v>
       </c>
       <c r="D63" t="str">
-        <v>043, 056</v>
+        <v>026</v>
       </c>
       <c r="E63" t="str">
         <v>Y</v>
       </c>
       <c r="F63" t="str">
-        <v>mentor-session-link.spec.ts</v>
+        <v>tips.spec.ts</v>
       </c>
       <c r="G63" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-09</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>FR-SP-04</v>
+        <v>FR-GM-04</v>
       </c>
       <c r="B64" t="str">
-        <v>AI reply-quality sweep</v>
+        <v>AI post-quality sweep</v>
       </c>
       <c r="C64" t="str">
         <v>Y</v>
@@ -4477,7 +4597,7 @@
         <v>Y</v>
       </c>
       <c r="F64" t="str">
-        <v>ai-quality-score.spec.ts, admin-sweep.spec.ts</v>
+        <v>ai-quality-score.spec.ts, admin-sweep.spec.ts, admin-digest-send.spec.ts</v>
       </c>
       <c r="G64" t="str">
         <v>2026-08-21</v>
@@ -4488,750 +4608,750 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FR-SP-05</v>
+        <v>FR-GM-05</v>
       </c>
       <c r="B65" t="str">
-        <v>Pre-publish moderation gate, fail-open with retry queue</v>
+        <v>Newsletter subscribe</v>
       </c>
       <c r="C65" t="str">
         <v>Y</v>
       </c>
       <c r="D65" t="str">
-        <v>098, 099</v>
+        <v>008</v>
       </c>
       <c r="E65" t="str">
         <v>Y</v>
       </c>
       <c r="F65" t="str">
-        <v>moderation.spec.ts</v>
+        <v>newsletter-and-search.spec.ts</v>
       </c>
       <c r="G65" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-07</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>2026-08-15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FR-SP-06</v>
+        <v>FR-GM-06</v>
       </c>
       <c r="B66" t="str">
-        <v>Community events + RSVP</v>
+        <v>Admin-triggered newsletter digest email send</v>
       </c>
       <c r="C66" t="str">
         <v>Y</v>
       </c>
       <c r="D66" t="str">
-        <v>100</v>
+        <v>052</v>
       </c>
       <c r="E66" t="str">
         <v>Y</v>
       </c>
       <c r="F66" t="str">
-        <v>events.spec.ts</v>
+        <v>admin-digest-send.spec.ts</v>
       </c>
       <c r="G66" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-21</v>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>FR-FA-01</v>
+        <v>FR-SP-01</v>
       </c>
       <c r="B67" t="str">
-        <v>Gig listing + checkout</v>
+        <v>Discussions + karma + anonymous posting</v>
       </c>
       <c r="C67" t="str">
         <v>Y</v>
       </c>
       <c r="D67" t="str">
-        <v>002, 029</v>
+        <v>009, 025, 027</v>
       </c>
       <c r="E67" t="str">
         <v>Y</v>
       </c>
       <c r="F67" t="str">
-        <v>auth-and-gigs.spec.ts, checkout-payment.spec.ts, gigs-filters.spec.ts</v>
+        <v>discussions.spec.ts, karma-and-anonymous.spec.ts</v>
       </c>
       <c r="G67" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-09</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-12 / 2026-08-16 / 2026-08-21</v>
+        <v>2026-08-11 / 2026-08-12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FR-FA-02</v>
+        <v>FR-SP-02</v>
       </c>
       <c r="B68" t="str">
-        <v>Order lifecycle + escrow + webhooks</v>
+        <v>Public members directory</v>
       </c>
       <c r="C68" t="str">
         <v>Y</v>
       </c>
       <c r="D68" t="str">
-        <v>002, 004, 029</v>
+        <v>035, 047</v>
       </c>
       <c r="E68" t="str">
         <v>Y</v>
       </c>
       <c r="F68" t="str">
-        <v>order-lifecycle.spec.ts, escrow-workflow.spec.ts, webhook-payment-captured.spec.ts</v>
+        <v>members.spec.ts</v>
       </c>
       <c r="G68" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-19</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-11 / 2026-08-12</v>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FR-FA-03</v>
+        <v>FR-SP-03</v>
       </c>
       <c r="B69" t="str">
-        <v>Order messaging + reviews</v>
+        <v>Mentor session links in community</v>
       </c>
       <c r="C69" t="str">
         <v>Y</v>
       </c>
       <c r="D69" t="str">
-        <v>005, 006</v>
+        <v>043, 056</v>
       </c>
       <c r="E69" t="str">
         <v>Y</v>
       </c>
       <c r="F69" t="str">
-        <v>order-history.spec.ts</v>
+        <v>mentor-session-link.spec.ts</v>
       </c>
       <c r="G69" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-22</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>FR-FA-04</v>
+        <v>FR-SP-04</v>
       </c>
       <c r="B70" t="str">
-        <v>Payout requests</v>
+        <v>AI reply-quality sweep</v>
       </c>
       <c r="C70" t="str">
         <v>Y</v>
       </c>
       <c r="D70" t="str">
-        <v>014, 020</v>
+        <v>048, 050</v>
       </c>
       <c r="E70" t="str">
         <v>Y</v>
       </c>
       <c r="F70" t="str">
-        <v>earnings-and-payouts.spec.ts</v>
+        <v>ai-quality-score.spec.ts, admin-sweep.spec.ts</v>
       </c>
       <c r="G70" t="str">
-        <v>2026-08-09</v>
+        <v>2026-08-21</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-11</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>FR-FA-05</v>
+        <v>FR-SP-05</v>
       </c>
       <c r="B71" t="str">
-        <v>Bidirectional gig skill ratings</v>
+        <v>Pre-publish moderation gate, fail-open with retry queue</v>
       </c>
       <c r="C71" t="str">
         <v>Y</v>
       </c>
       <c r="D71" t="str">
-        <v>054</v>
+        <v>098, 099</v>
       </c>
       <c r="E71" t="str">
         <v>Y</v>
       </c>
       <c r="F71" t="str">
-        <v>skill-ratings.spec.ts</v>
+        <v>moderation.spec.ts</v>
       </c>
       <c r="G71" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-22</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>FR-FA-06</v>
+        <v>FR-SP-06</v>
       </c>
       <c r="B72" t="str">
-        <v>AI delivery-quality review</v>
+        <v>Community events + RSVP</v>
       </c>
       <c r="C72" t="str">
         <v>Y</v>
       </c>
       <c r="D72" t="str">
-        <v>048</v>
+        <v>100</v>
       </c>
       <c r="E72" t="str">
         <v>Y</v>
       </c>
       <c r="F72" t="str">
-        <v>ai-quality-score.spec.ts</v>
+        <v>events.spec.ts</v>
       </c>
       <c r="G72" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-21</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>FR-FA-07</v>
+        <v>FR-FA-01</v>
       </c>
       <c r="B73" t="str">
-        <v>Experience-gated gig pricing</v>
+        <v>Gig listing + checkout</v>
       </c>
       <c r="C73" t="str">
         <v>Y</v>
       </c>
       <c r="D73" t="str">
-        <v>039</v>
+        <v>002, 029</v>
       </c>
       <c r="E73" t="str">
         <v>Y</v>
       </c>
       <c r="F73" t="str">
-        <v>experience-gate.spec.ts</v>
+        <v>auth-and-gigs.spec.ts, checkout-payment.spec.ts, gigs-filters.spec.ts</v>
       </c>
       <c r="G73" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-10</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-12 / 2026-08-16 / 2026-08-21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>FR-FA-08</v>
+        <v>FR-FA-02</v>
       </c>
       <c r="B74" t="str">
-        <v>FlexPro Pro subscription gates posting (either side)</v>
+        <v>Order lifecycle + escrow + webhooks</v>
       </c>
       <c r="C74" t="str">
         <v>Y</v>
       </c>
       <c r="D74" t="str">
-        <v>093, 094</v>
+        <v>002, 004, 029</v>
       </c>
       <c r="E74" t="str">
         <v>Y</v>
       </c>
       <c r="F74" t="str">
-        <v>client-jobs.spec.ts</v>
+        <v>order-lifecycle.spec.ts, escrow-workflow.spec.ts, webhook-payment-captured.spec.ts</v>
       </c>
       <c r="G74" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-10</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>2026-08-11 / 2026-08-12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>FR-FA-09</v>
+        <v>FR-FA-03</v>
       </c>
       <c r="B75" t="str">
-        <v>Client job posting + free application + accept/reject</v>
+        <v>Order messaging + reviews</v>
       </c>
       <c r="C75" t="str">
         <v>Y</v>
       </c>
       <c r="D75" t="str">
-        <v>093</v>
+        <v>005, 006</v>
       </c>
       <c r="E75" t="str">
         <v>Y</v>
       </c>
       <c r="F75" t="str">
-        <v>client-jobs.spec.ts</v>
+        <v>order-history.spec.ts</v>
       </c>
       <c r="G75" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-07</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>FR-FA-10</v>
+        <v>FR-FA-04</v>
       </c>
       <c r="B76" t="str">
-        <v>2% service fee, both sides, on accepted transaction</v>
+        <v>Payout requests</v>
       </c>
       <c r="C76" t="str">
         <v>Y</v>
       </c>
       <c r="D76" t="str">
-        <v>093</v>
+        <v>014, 020</v>
       </c>
       <c r="E76" t="str">
         <v>Y</v>
       </c>
       <c r="F76" t="str">
-        <v>client-jobs.spec.ts</v>
+        <v>earnings-and-payouts.spec.ts</v>
       </c>
       <c r="G76" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-09</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>2026-08-11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>FR-FA-11</v>
+        <v>FR-FA-05</v>
       </c>
       <c r="B77" t="str">
-        <v>Bidirectional order disputes (buyer or seller)</v>
+        <v>Bidirectional gig skill ratings</v>
       </c>
       <c r="C77" t="str">
         <v>Y</v>
       </c>
       <c r="D77" t="str">
-        <v>093</v>
+        <v>054</v>
       </c>
       <c r="E77" t="str">
         <v>Y</v>
       </c>
       <c r="F77" t="str">
-        <v>dispute route fix, direct verification</v>
+        <v>skill-ratings.spec.ts</v>
       </c>
       <c r="G77" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-22</v>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>FR-FA-12</v>
+        <v>FR-FA-06</v>
       </c>
       <c r="B78" t="str">
-        <v>3-tier posting subscription + admin-configurable price/credits, credit-metered gig/job posting</v>
+        <v>AI delivery-quality review</v>
       </c>
       <c r="C78" t="str">
         <v>Y</v>
       </c>
       <c r="D78" t="str">
-        <v>096</v>
+        <v>048</v>
       </c>
       <c r="E78" t="str">
         <v>Y</v>
       </c>
       <c r="F78" t="str">
-        <v>subscription-tiers.spec.ts</v>
+        <v>ai-quality-score.spec.ts</v>
       </c>
       <c r="G78" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-20</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>FR-FA-13</v>
+        <v>FR-FA-07</v>
       </c>
       <c r="B79" t="str">
-        <v>AI gig-listing quality assist at post-time (informational, uncredited)</v>
+        <v>Experience-gated gig pricing</v>
       </c>
       <c r="C79" t="str">
         <v>Y</v>
       </c>
       <c r="D79" t="str">
-        <v>097</v>
+        <v>039</v>
       </c>
       <c r="E79" t="str">
         <v>Y</v>
       </c>
       <c r="F79" t="str">
-        <v>dashboard-activity-and-gig-quality.spec.ts</v>
+        <v>experience-gate.spec.ts</v>
       </c>
       <c r="G79" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-17</v>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>2026-08-17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>FR-SE-01</v>
+        <v>FR-FA-08</v>
       </c>
       <c r="B80" t="str">
-        <v>Projects + asks + applications</v>
+        <v>FlexPro Pro subscription gates posting (either side)</v>
       </c>
       <c r="C80" t="str">
         <v>Y</v>
       </c>
       <c r="D80" t="str">
-        <v>030, 047</v>
+        <v>093, 094</v>
       </c>
       <c r="E80" t="str">
         <v>Y</v>
       </c>
       <c r="F80" t="str">
-        <v>projects-and-asks.spec.ts, applications.spec.ts</v>
+        <v>client-jobs.spec.ts</v>
       </c>
       <c r="G80" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-19</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>FR-SE-02</v>
+        <v>FR-FA-09</v>
       </c>
       <c r="B81" t="str">
-        <v>Accept/decline/close ask + notify</v>
+        <v>Client job posting + free application + accept/reject</v>
       </c>
       <c r="C81" t="str">
         <v>Y</v>
       </c>
       <c r="D81" t="str">
-        <v>030, 051</v>
+        <v>093</v>
       </c>
       <c r="E81" t="str">
         <v>Y</v>
       </c>
       <c r="F81" t="str">
-        <v>ask-close.spec.ts, applications.spec.ts</v>
+        <v>client-jobs.spec.ts</v>
       </c>
       <c r="G81" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-19 / 2026-08-21</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>FR-SE-03</v>
+        <v>FR-FA-10</v>
       </c>
       <c r="B82" t="str">
-        <v>AI + human verification scoring + gated self-submission</v>
+        <v>2% service fee, both sides, on accepted transaction</v>
       </c>
       <c r="C82" t="str">
         <v>Y</v>
       </c>
       <c r="D82" t="str">
-        <v>031, 032, 033, 034, 048</v>
+        <v>093</v>
       </c>
       <c r="E82" t="str">
         <v>Y</v>
       </c>
       <c r="F82" t="str">
-        <v>verification.spec.ts, project-shipped.spec.ts</v>
+        <v>client-jobs.spec.ts</v>
       </c>
       <c r="G82" t="str">
-        <v>2026-08-20</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-20</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>FR-SE-04</v>
+        <v>FR-FA-11</v>
       </c>
       <c r="B83" t="str">
-        <v>Public verified-outcome track record</v>
+        <v>Bidirectional order disputes (buyer or seller)</v>
       </c>
       <c r="C83" t="str">
         <v>Y</v>
       </c>
       <c r="D83" t="str">
-        <v>031</v>
+        <v>093</v>
       </c>
       <c r="E83" t="str">
         <v>Y</v>
       </c>
       <c r="F83" t="str">
-        <v>track-record.spec.ts, project-shipped.spec.ts</v>
+        <v>dispute route fix, direct verification</v>
       </c>
       <c r="G83" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-19 / 2026-08-20</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>FR-SE-05</v>
+        <v>FR-FA-12</v>
       </c>
       <c r="B84" t="str">
-        <v>Public People directory</v>
+        <v>3-tier posting subscription + admin-configurable price/credits, credit-metered gig/job posting</v>
       </c>
       <c r="C84" t="str">
         <v>Y</v>
       </c>
       <c r="D84" t="str">
-        <v>035, 036, 047</v>
+        <v>096</v>
       </c>
       <c r="E84" t="str">
         <v>Y</v>
       </c>
       <c r="F84" t="str">
-        <v>people-directory.spec.ts</v>
+        <v>subscription-tiers.spec.ts</v>
       </c>
       <c r="G84" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-19</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>FR-SE-06</v>
+        <v>FR-FA-13</v>
       </c>
       <c r="B85" t="str">
-        <v>Bidirectional build skill ratings</v>
+        <v>AI gig-listing quality assist at post-time (informational, uncredited)</v>
       </c>
       <c r="C85" t="str">
         <v>Y</v>
       </c>
       <c r="D85" t="str">
-        <v>054</v>
+        <v>097</v>
       </c>
       <c r="E85" t="str">
         <v>Y</v>
       </c>
       <c r="F85" t="str">
-        <v>skill-ratings.spec.ts</v>
+        <v>dashboard-activity-and-gig-quality.spec.ts</v>
       </c>
       <c r="G85" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-02</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-22</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>FR-SE-07</v>
+        <v>FR-SE-01</v>
       </c>
       <c r="B86" t="str">
-        <v>Admin LLM provider/flag management</v>
+        <v>Projects + asks + applications</v>
       </c>
       <c r="C86" t="str">
         <v>Y</v>
       </c>
       <c r="D86" t="str">
-        <v>048, 050</v>
+        <v>030, 047</v>
       </c>
       <c r="E86" t="str">
         <v>Y</v>
       </c>
       <c r="F86" t="str">
-        <v>admin-llm.spec.ts</v>
+        <v>projects-and-asks.spec.ts, applications.spec.ts</v>
       </c>
       <c r="G86" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-19</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>FR-RM-01</v>
+        <v>FR-SE-02</v>
       </c>
       <c r="B87" t="str">
-        <v>Mentor cohorts, packages, recording resale</v>
+        <v>Accept/decline/close ask + notify</v>
       </c>
       <c r="C87" t="str">
         <v>Y</v>
       </c>
       <c r="D87" t="str">
-        <v>062</v>
+        <v>030, 051</v>
       </c>
       <c r="E87" t="str">
         <v>Y</v>
       </c>
       <c r="F87" t="str">
-        <v>mentor-monetization.spec.ts</v>
+        <v>ask-close.spec.ts, applications.spec.ts</v>
       </c>
       <c r="G87" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-21</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-19 / 2026-08-21</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>FR-RM-02</v>
+        <v>FR-SE-03</v>
       </c>
       <c r="B88" t="str">
-        <v>Public StackWorks track-record badge</v>
+        <v>AI + human verification scoring + gated self-submission</v>
       </c>
       <c r="C88" t="str">
         <v>Y</v>
       </c>
       <c r="D88" t="str">
-        <v>060</v>
+        <v>031, 032, 033, 034, 048</v>
       </c>
       <c r="E88" t="str">
         <v>Y</v>
       </c>
       <c r="F88" t="str">
-        <v>track-record-badge.spec.ts</v>
+        <v>verification.spec.ts, project-shipped.spec.ts</v>
       </c>
       <c r="G88" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-20</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>FR-RM-03</v>
+        <v>FR-SE-04</v>
       </c>
       <c r="B89" t="str">
-        <v>FlexPro Top Tier badge</v>
+        <v>Public verified-outcome track record</v>
       </c>
       <c r="C89" t="str">
         <v>Y</v>
       </c>
       <c r="D89" t="str">
-        <v>036</v>
+        <v>031</v>
       </c>
       <c r="E89" t="str">
         <v>Y</v>
       </c>
       <c r="F89" t="str">
-        <v>top-tier-badge.spec.ts, top-tier-badge-positive.spec.ts (also fixed a real bug: was checking freeagent_headcount, a platform-wide constant, instead of freeagent_evidence, this seller's own review count)</v>
+        <v>track-record.spec.ts, project-shipped.spec.ts</v>
       </c>
       <c r="G89" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-15</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-19 / 2026-08-20</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>FR-RM-04</v>
+        <v>FR-SE-05</v>
       </c>
       <c r="B90" t="str">
-        <v>GreyMatters cross-posting to DeepEdge</v>
+        <v>Public People directory</v>
       </c>
       <c r="C90" t="str">
         <v>Y</v>
       </c>
       <c r="D90" t="str">
-        <v>none</v>
+        <v>035, 036, 047</v>
       </c>
       <c r="E90" t="str">
         <v>Y</v>
       </c>
       <c r="F90" t="str">
-        <v>greymatters-cross-posting.spec.ts</v>
+        <v>people-directory.spec.ts</v>
       </c>
       <c r="G90" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-19</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>FR-RM-05</v>
+        <v>FR-SE-06</v>
       </c>
       <c r="B91" t="str">
-        <v>DeepEdge sitemap + JobPosting JSON-LD</v>
+        <v>Bidirectional build skill ratings</v>
       </c>
       <c r="C91" t="str">
         <v>Y</v>
       </c>
       <c r="D91" t="str">
-        <v>none</v>
+        <v>054</v>
       </c>
       <c r="E91" t="str">
         <v>Y</v>
       </c>
       <c r="F91" t="str">
-        <v>seo.spec.ts</v>
+        <v>skill-ratings.spec.ts</v>
       </c>
       <c r="G91" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-22</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-22</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>FR-RM-06</v>
+        <v>FR-SE-07</v>
       </c>
       <c r="B92" t="str">
-        <v>In-app weekly digest</v>
+        <v>Admin LLM provider/flag management</v>
       </c>
       <c r="C92" t="str">
         <v>Y</v>
       </c>
       <c r="D92" t="str">
-        <v>none</v>
+        <v>048, 050</v>
       </c>
       <c r="E92" t="str">
         <v>Y</v>
       </c>
       <c r="F92" t="str">
-        <v>weekly-digest.spec.ts</v>
+        <v>admin-llm.spec.ts</v>
       </c>
       <c r="G92" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-21</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>FR-RM-07</v>
+        <v>FR-RM-01</v>
       </c>
       <c r="B93" t="str">
-        <v>Salary trend watch/alerts</v>
+        <v>Mentor cohorts, packages, recording resale</v>
       </c>
       <c r="C93" t="str">
         <v>Y</v>
       </c>
       <c r="D93" t="str">
-        <v>063</v>
+        <v>062</v>
       </c>
       <c r="E93" t="str">
         <v>Y</v>
       </c>
       <c r="F93" t="str">
-        <v>salary-trend-watch.spec.ts, salary-trend-alert-fires.spec.ts</v>
+        <v>mentor-monetization.spec.ts</v>
       </c>
       <c r="G93" t="str">
         <v>2026-08-23</v>
@@ -5242,163 +5362,319 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FR-RM-08</v>
+        <v>FR-RM-02</v>
       </c>
       <c r="B94" t="str">
-        <v>Job salary_disclosed checkbox (create + edit)</v>
+        <v>Public StackWorks track-record badge</v>
       </c>
       <c r="C94" t="str">
         <v>Y</v>
       </c>
       <c r="D94" t="str">
-        <v>none</v>
+        <v>060</v>
       </c>
       <c r="E94" t="str">
         <v>Y</v>
       </c>
       <c r="F94" t="str">
-        <v>salary-trend-alert-fires.spec.ts</v>
+        <v>track-record-badge.spec.ts</v>
       </c>
       <c r="G94" t="str">
         <v>2026-08-23</v>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>FR-LL-01</v>
+        <v>FR-RM-03</v>
       </c>
       <c r="B95" t="str">
-        <v>Anonymized future-role posting</v>
+        <v>FlexPro Top Tier badge</v>
       </c>
       <c r="C95" t="str">
         <v>Y</v>
       </c>
       <c r="D95" t="str">
-        <v>087</v>
+        <v>036</v>
       </c>
       <c r="E95" t="str">
         <v>Y</v>
       </c>
       <c r="F95" t="str">
-        <v>longlist-future-roles.spec.ts (cross-platform)</v>
+        <v>top-tier-badge.spec.ts, top-tier-badge-positive.spec.ts (also fixed a real bug: was checking freeagent_headcount, a platform-wide constant, instead of freeagent_evidence, this seller's own review count)</v>
       </c>
       <c r="G95" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-17</v>
       </c>
       <c r="H95" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>FR-LL-02</v>
+        <v>FR-RM-04</v>
       </c>
       <c r="B96" t="str">
-        <v>Subscribe as future-interested</v>
+        <v>GreyMatters cross-posting to DeepEdge</v>
       </c>
       <c r="C96" t="str">
         <v>Y</v>
       </c>
       <c r="D96" t="str">
-        <v>087, 088</v>
+        <v>none</v>
       </c>
       <c r="E96" t="str">
         <v>Y</v>
       </c>
       <c r="F96" t="str">
-        <v>longlist-future-roles.spec.ts (cross-platform)</v>
+        <v>greymatters-cross-posting.spec.ts</v>
       </c>
       <c r="G96" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>FR-LL-03</v>
+        <v>FR-RM-05</v>
       </c>
       <c r="B97" t="str">
-        <v>Member-stated future interests</v>
+        <v>DeepEdge sitemap + JobPosting JSON-LD</v>
       </c>
       <c r="C97" t="str">
         <v>Y</v>
       </c>
       <c r="D97" t="str">
-        <v>087</v>
+        <v>none</v>
       </c>
       <c r="E97" t="str">
         <v>Y</v>
       </c>
       <c r="F97" t="str">
-        <v>profile-future-interests.spec.ts</v>
+        <v>seo.spec.ts</v>
       </c>
       <c r="G97" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>FR-LL-04</v>
+        <v>FR-RM-06</v>
       </c>
       <c r="B98" t="str">
-        <v>AI-surfaced second candidate set</v>
+        <v>In-app weekly digest</v>
       </c>
       <c r="C98" t="str">
         <v>Y</v>
       </c>
       <c r="D98" t="str">
-        <v>087</v>
+        <v>none</v>
       </c>
       <c r="E98" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F98" t="str">
-        <v>not covered -- flag defaults off; needs an admin-enabled-flag spec as a follow-up</v>
+        <v>weekly-digest.spec.ts</v>
       </c>
       <c r="G98" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-23</v>
       </c>
       <c r="H98" t="str">
-        <v/>
+        <v>2026-08-23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>FR-RM-07</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Salary trend watch/alerts</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D99" t="str">
+        <v>063</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F99" t="str">
+        <v>salary-trend-watch.spec.ts, salary-trend-alert-fires.spec.ts</v>
+      </c>
+      <c r="G99" t="str">
+        <v>2026-08-23</v>
+      </c>
+      <c r="H99" t="str">
+        <v>2026-08-23</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FR-RM-08</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Job salary_disclosed checkbox (create + edit)</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D100" t="str">
+        <v>none</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F100" t="str">
+        <v>salary-trend-alert-fires.spec.ts</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2026-08-23</v>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>FR-LL-01</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Anonymized future-role posting</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D101" t="str">
+        <v>087</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F101" t="str">
+        <v>longlist-future-roles.spec.ts (cross-platform)</v>
+      </c>
+      <c r="G101" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>FR-LL-02</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Subscribe as future-interested</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D102" t="str">
+        <v>087, 088</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F102" t="str">
+        <v>longlist-future-roles.spec.ts (cross-platform)</v>
+      </c>
+      <c r="G102" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>FR-LL-03</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Member-stated future interests</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D103" t="str">
+        <v>087</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F103" t="str">
+        <v>profile-future-interests.spec.ts</v>
+      </c>
+      <c r="G103" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>FR-LL-04</v>
+      </c>
+      <c r="B104" t="str">
+        <v>AI-surfaced second candidate set (was completely non-functional since launch -- platform_people_index missing 2 columns, fixed 111)</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D104" t="str">
+        <v>087, 111</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F104" t="str">
+        <v>longlist-role-lifecycle-and-matching.spec.ts</v>
+      </c>
+      <c r="G104" t="str">
+        <v>2026-08-23</v>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>FR-LL-05</v>
       </c>
-      <c r="B99" t="str">
-        <v>Role filled/expired + subscriber notification</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Y</v>
-      </c>
-      <c r="D99" t="str">
-        <v>087</v>
-      </c>
-      <c r="E99" t="str">
-        <v>N</v>
-      </c>
-      <c r="F99" t="str">
-        <v>not covered -- follow-up</v>
-      </c>
-      <c r="G99" t="str">
-        <v>2026-09-01</v>
-      </c>
-      <c r="H99" t="str">
+      <c r="B105" t="str">
+        <v>Role filled/expired + subscriber notification (expired never notified, no UI to reach it -- both fixed)</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D105" t="str">
+        <v>087, 110</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F105" t="str">
+        <v>longlist-role-lifecycle-and-matching.spec.ts</v>
+      </c>
+      <c r="G105" t="str">
+        <v>2026-08-23</v>
+      </c>
+      <c r="H105" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H105"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5632,7 +5908,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E51"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -6346,7 +6622,7 @@
         <v>Done, all 3 apps, all 3 tiers, live and e2e-verified</v>
       </c>
       <c r="C42" t="str">
-        <v>Mid-task follow-up to the 2026-09-01 rebrand (see the row above this one), which had deliberately limited scope to the brand/domain layer and left every internal identifier (folder names, Docker image tags, Swarm service keys, Traefik router IDs, e2e codenames, live DB literal values) on the old codenames -- "renaming those would touch dozens of files for zero user-facing benefit and meaningfully risk the 125-spec e2e suite." User asked to revisit that call. A preliminary grep undersold the true scope (172+ files, live production data across 6+ tables/views/functions, Swarm service recreation) -- surfaced honestly before proceeding rather than acted on the original under-scoped ask, then re-asked with the real numbers: whether to go infra-only, +source-code, or +live-DB-data (user chose all three, for all three apps, including the two even-older divergences this surfaced along the way -- stackedge's own earlier rename from Prolab, and DeepEdge's still-older ExpertEdge Traefik layer). Executed one app fully (all 3 tiers, deployed, e2e-verified) before starting the next, per the approved plan, in order: FlexPro (smallest), StackWorks (largest live-data footprint), DeepEdge (largest code blast radius, most cross-app links). Per app: Tier 0 (fix independent bugs found in files this pass already touches), Tier 1 (folder/image/Swarm-service/Traefik rename -- a genuine new-service creation, not an in-place update, so the old service is only removed after the new one is confirmed healthy on the real domain), Tier 2 (e2e directory/helper-function/test-user-prefix rename plus the shared PILLARS-array pillar-key rename duplicated across all 7 apps' EcosystemWidget.tsx/EcosystemSearchResults.tsx/FeedCard.tsx/notification-link.ts), Tier 3 (the live-data migration -- deliberately shipped in the SAME deploy as Tier 2's app code, never before it, since the two are only individually safe together: old code writing the old literal after the constraint stops allowing it, or new code writing the new literal before the constraint allows it, both break real traffic). For each app's Tier 3, an Explore agent first catalogued every live DB object (tables/columns/constraints/function bodies/views/seed data) touching the old literal by reading the LATEST authoritative definition across all existing migration files, cross-checked against the live database directly (pg_constraint, pg_depend, pg_class.reloptions, real row counts) rather than trusting migration-file history alone -- this caught real drift a file-only read would have missed, e.g. migration 089's own CREATE OR REPLACE VIEW silently dropping a security_invoker=true flag 067 had set on the collaborators view, unrelated to this rename and left alone, just flagged. Every migration was dry-run inside a transaction that rolled back before being applied for real. FlexPro (103, 104): renamed the freeagent_subscriptions table, its 7 auto-generated constraint/index names (Postgres does not rename these along with a table, confirmed the hard way), handle_email_confirmed(), get_active_tier_id() (a plpgsql function body is opaque text re-resolved by name on each replan, unlike a view or RLS-policy qual which are OID-bound and transparently follow a table rename -- so this one specifically had to have both its literal AND its table reference updated together, or it would have started throwing "relation does not exist" on next call), and the greyin_scores view's freeagent_score/evidence/headcount output columns, which CREATE OR REPLACE VIEW cannot rename in place (columns must keep exact name+position) -- required DROP VIEW...CASCADE, which turned out to cascade to 5 objects, not the 1 the initial dependency check found: platform_people_index (a view) plus 4 RLS policies on posts/comments gating on greyin_scores.is_verified_expert, all recreated verbatim since none read the renamed columns specifically. StackWorks (105): same shape, plus a second orphaned identifier this app carried from an even earlier rename that 047 (StackEdge&lt;-Prolab) never fully closed -- the CHECK constraint governing profiles.stackedge_role was still literally named profiles_prolab_role_check, 047's own comment having wrongly assumed RENAME COLUMN would also rename the constraint (it silently doesn't); fixed properly this time rather than carried forward again. DeepEdge (106): notably simpler at the DB layer -- this app has no per-app profile column and, unlike FlexPro/StackWorks, is not one of the scored pillars inside greyin_scores at all, so no CASCADE was needed -- but resolved its own two-literal inconsistency (my_pillar_activity used 'expertedge' while platform_search_index/activity_feed used 'greyin' for the identical app, a mismatch 053_activity_feed.sql's own comment had already flagged as pre-existing; both now say 'deepedge'). Careful disambiguation was required throughout DeepEdge's pass specifically: the bare pillar-key literal 'greyin' (in scope, this app's own tag) had to be distinguished from greyin_score/greyin_scores (the platform-wide composite reputation system, out of scope), greyin_hub (a different app's own separate pillar tag, out of scope), and the greyin.net domain/SSO cookie domain (out of scope) -- done via exact colon/quote-bounded substring matching (`greyin:` / `'greyin'`) which structurally cannot match `greyin_hub:`/`greyin_score`/`greyin.net`, verified afterward with zero casualties against any of the three. Real, independent bugs found and fixed along the way (Tier 0, or found-in-passing and fixed with the user's explicit go-ahead once the true size became clear): three separate broken deploy-script domain env-var references (FREEAGENT_DOMAIN/STACKEDGE_DOMAIN/EXPERTEDGE_DOMAIN, none of which exist in deployment/.env, which now only has FLEXPRO_DOMAIN/STACKWORKS_DOMAIN/DEEPEDGE_DOMAIN -- all three would have baked an empty NEXT_PUBLIC_SITE_URL had the script been run as-is); StackWorks' public, hotlinkable SVG track-record badge still rendering the literal text "STACKEDGE VERIFIED"; DeepEdge's lib/email.ts hardcoding "Greyin" instead of "DeepEdge" in transactional email sender name/header/footer/referral copy, plus discovering the identical class of bug for FlexPro along the way -- both apps' frontend-stack.yml environment blocks were passing the generic shared ${SMTP_SENDER_NAME} ("Greyin Platform") instead of an app-specific override, silently no-op'ing each app's own code-level brand fallback; and, the largest of these, DeepEdge's own pages (nav header logo, page title, terms/privacy copy, ~40 files) still literally saying "Greyin" instead of "DeepEdge" throughout -- the 2026-09-01 brand-only rebrand never actually reached this app's own self-identification, only its domain and a few pages. Surfaced to the user as a scope question given the size (found while sweeping deepedge/src for the pillar-key rename, unrelated to it) rather than silently fixed or silently skipped; approved, then fixed via a surgical `&gt;Greyin&lt;` substring pattern (logo/title text is always the entire tag content with nothing else in it; every legitimate platform-wide reference -- "Greyin Score", "the wider Greyin ecosystem", "Back to the Greyin ecosystem hub", the shared "More across Greyin"/"People on Greyin" cross-pillar widgets duplicated in every app -- is always multi-word and so structurally untouched by that pattern), followed by roughly 40 individual file-by-file judgment calls for the remainder; deepedge/src/app/about/page.tsx was found already doing the self-brand-vs-platform-wide distinction correctly and needed zero changes, evidence the pattern is real craft, not just neglect throughout. Deploy sequencing lessons carried forward from FlexPro into the later two apps: PostgREST's NOTIFY pgrst reload only reliably refreshes read-routing, not write-routing, for a renamed table -- POST requests 404'd against the correctly-renamed, correctly-queryable-via-GET flexpro_subscriptions table until docker service update --force supabase_rest (an actual restart) was run; StackWorks and DeepEdge's migrations both proactively included that restart rather than waiting to rediscover it. A second, new deploy gotcha surfaced during DeepEdge's cutover specifically: briefly having both the old service (its Traefik router still on the even-older `expertedge` ID) and the new `deepedge_web` service live simultaneously, both bound to the identical Host(`deepedge.greyin.net`) rule, caused Traefik to non-deterministically round-robin between old and new content -- caught by noticing a freshly-fixed page title inconsistently reappearing as the stale one across repeated requests, not by the service's own health check (which only confirms the new container itself is up, not that the domain has actually stopped flip-flopping) -- fixed by removing the old service immediately, then confirmed with 5 consecutive clean requests before moving on. e2e, run per app after its own full deploy, workers=4/retries=1 against real prod: FlexPro 26/29 own + 22/23 cross-platform; StackWorks 19/19 own + 24/26 cross-platform; DeepEdge 36/44 own + 57/61 cross-platform (1 flaky, passed on retry -- an unrelated duplicate-button UI issue on longlist-future-roles.spec.ts). Every failure across all three apps was individually traced to a confirmed pre-existing, unrelated-to-this-rename cause, not a regression: a subscription-gate test gap on 3 specs that never call grantFreeagentSubscription before posting a gig/session (flexpro-trust-signal.spec.ts, mentor-sessions.spec.ts, mentor-monetization.spec.ts), and a freshly-signed-up candidate's row not reliably showing up yet on /candidates search or /candidates/{id} profile pages within the test's timeout, affecting most of DeepEdge's own suite plus 2 cross-platform specs -- proven unrelated by reproducing identically on candidates.spec.ts, a completely untouched baseline test, and by directly querying greyin_scores/is_verified_expert via REST and confirming the underlying mechanism returns correct data for existing users; likely a signup-trigger propagation race, the same general shape as issues e2e/utils/admin.ts already documents elsewhere -- flagged as a dedicated follow-up, not fixed here as out of scope for a naming rename. One image-upload.spec.ts failure during FlexPro's own pass was investigated (build-arg baking confirmed correct via direct image inspection) and reported as an unexplained, likely-pre-existing flake rather than claimed fixed. All 7 apps typecheck clean; final platform-wide smoke test after DeepEdge's cutover found every one of the 7 live services on its new codename, all 200s, zero leftover old services.</v>
+        <v>Mid-task follow-up to the 2026-09-01 rebrand (see the row above this one), which had deliberately limited scope to the brand/domain layer and left every internal identifier (folder names, Docker image tags, Swarm service keys, Traefik router IDs, e2e codenames, live DB literal values) on the old codenames -- "renaming those would touch dozens of files for zero user-facing benefit and meaningfully risk the 125-spec e2e suite." User asked to revisit that call. A preliminary grep undersold the true scope (172+ files, live production data across 6+ tables/views/functions, Swarm service recreation) -- surfaced honestly before proceeding rather than acted on the original under-scoped ask, then re-asked with the real numbers: whether to go infra-only, +source-code, or +live-DB-data (user chose all three, for all three apps, including the two even-older divergences this surfaced along the way -- stackedge's own earlier rename from Prolab, and DeepEdge's still-older ExpertEdge Traefik layer). Executed one app fully (all 3 tiers, deployed, e2e-verified) before starting the next, per the approved plan, in order: FlexPro (smallest), StackWorks (largest live-data footprint), DeepEdge (largest code blast radius, most cross-app links). Per app: Tier 0 (fix independent bugs found in files this pass already touches), Tier 1 (folder/image/Swarm-service/Traefik rename -- a genuine new-service creation, not an in-place update, so the old service is only removed after the new one is confirmed healthy on the real domain), Tier 2 (e2e directory/helper-function/test-user-prefix rename plus the shared PILLARS-array pillar-key rename duplicated across all 7 apps' EcosystemWidget.tsx/EcosystemSearchResults.tsx/FeedCard.tsx/notification-link.ts), Tier 3 (the live-data migration -- deliberately shipped in the SAME deploy as Tier 2's app code, never before it, since the two are only individually safe together: old code writing the old literal after the constraint stops allowing it, or new code writing the new literal before the constraint allows it, both break real traffic). For each app's Tier 3, an Explore agent first catalogued every live DB object (tables/columns/constraints/function bodies/views/seed data) touching the old literal by reading the LATEST authoritative definition across all existing migration files, cross-checked against the live database directly (pg_constraint, pg_depend, pg_class.reloptions, real row counts) rather than trusting migration-file history alone -- this caught real drift a file-only read would have missed, e.g. migration 089's own CREATE OR REPLACE VIEW silently dropping a security_invoker=true flag 067 had set on the collaborators view, unrelated to this rename and left alone, just flagged. Every migration was dry-run inside a transaction that rolled back before being applied for real. FlexPro (103, 104): renamed the freeagent_subscriptions table, its 7 auto-generated constraint/index names (Postgres does not rename these along with a table, confirmed the hard way), handle_email_confirmed(), get_active_tier_id() (a plpgsql function body is opaque text re-resolved by name on each replan, unlike a view or RLS-policy qual which are OID-bound and transparently follow a table rename -- so this one specifically had to have both its literal AND its table reference updated together, or it would have started throwing "relation does not exist" on next call), and the greyin_scores view's freeagent_score/evidence/headcount output columns, which CREATE OR REPLACE VIEW cannot rename in place (columns must keep exact name+position) -- required DROP VIEW...CASCADE, which turned out to cascade to 5 objects, not the 1 the initial dependency check found: platform_people_index (a view) plus 4 RLS policies on posts/comments gating on greyin_scores.is_verified_expert, all recreated verbatim since none read the renamed columns specifically. StackWorks (105): same shape, plus a second orphaned identifier this app carried from an even earlier rename that 047 (StackEdge&lt;-Prolab) never fully closed -- the CHECK constraint governing profiles.stackedge_role was still literally named profiles_prolab_role_check, 047's own comment having wrongly assumed RENAME COLUMN would also rename the constraint (it silently doesn't); fixed properly this time rather than carried forward again. DeepEdge (106): notably simpler at the DB layer -- this app has no per-app profile column and, unlike FlexPro/StackWorks, is not one of the scored pillars inside greyin_scores at all, so no CASCADE was needed -- but resolved its own two-literal inconsistency (my_pillar_activity used 'expertedge' while platform_search_index/activity_feed used 'greyin' for the identical app, a mismatch 053_activity_feed.sql's own comment had already flagged as pre-existing; both now say 'deepedge'). Careful disambiguation was required throughout DeepEdge's pass specifically: the bare pillar-key literal 'greyin' (in scope, this app's own tag) had to be distinguished from greyin_score/greyin_scores (the platform-wide composite reputation system, out of scope), greyin_hub (a different app's own separate pillar tag, out of scope), and the greyin.net domain/SSO cookie domain (out of scope) -- done via exact colon/quote-bounded substring matching (`greyin:` / `'greyin'`) which structurally cannot match `greyin_hub:`/`greyin_score`/`greyin.net`, verified afterward with zero casualties against any of the three. Real, independent bugs found and fixed along the way (Tier 0, or found-in-passing and fixed with the user's explicit go-ahead once the true size became clear): three separate broken deploy-script domain env-var references (FREEAGENT_DOMAIN/STACKEDGE_DOMAIN/EXPERTEDGE_DOMAIN, none of which exist in deployment/.env, which now only has FLEXPRO_DOMAIN/STACKWORKS_DOMAIN/DEEPEDGE_DOMAIN -- all three would have baked an empty NEXT_PUBLIC_SITE_URL had the script been run as-is); StackWorks' public, hotlinkable SVG track-record badge still rendering the literal text "STACKEDGE VERIFIED"; DeepEdge's lib/email.ts hardcoding "Greyin" instead of "DeepEdge" in transactional email sender name/header/footer/referral copy, plus discovering the identical class of bug for FlexPro along the way -- both apps' frontend-stack.yml environment blocks were passing the generic shared ${SMTP_SENDER_NAME} ("Greyin Platform") instead of an app-specific override, silently no-op'ing each app's own code-level brand fallback; and, the largest of these, DeepEdge's own pages (nav header logo, page title, terms/privacy copy, ~40 files) still literally saying "Greyin" instead of "DeepEdge" throughout -- the 2026-09-01 brand-only rebrand never actually reached this app's own self-identification, only its domain and a few pages. Surfaced to the user as a scope question given the size (found while sweeping deepedge/src for the pillar-key rename, unrelated to it) rather than silently fixed or silently skipped; approved, then fixed via a surgical `&gt;Greyin&lt;` substring pattern (logo/title text is always the entire tag content with nothing else in it; every legitimate platform-wide reference -- "Greyin Score", "the wider Greyin ecosystem", "Back to the Greyin ecosystem hub", the shared "More across Greyin"/"People on Greyin" cross-pillar widgets duplicated in every app -- is always multi-word and so structurally untouched by that pattern), followed by roughly 40 individual file-by-file judgment calls for the remainder; deepedge/src/app/about/page.tsx was found already doing the self-brand-vs-platform-wide distinction correctly and needed zero changes, evidence the pattern is real craft, not just neglect throughout. Deploy sequencing lessons carried forward from FlexPro into the later two apps: PostgREST's NOTIFY pgrst reload only reliably refreshes read-routing, not write-routing, for a renamed table -- POST requests 404'd against the correctly-renamed, correctly-queryable-via-GET flexpro_subscriptions table until docker service update --force supabase_rest (an actual restart) was run; StackWorks and DeepEdge's migrations both proactively included that restart rather than waiting to rediscover it. A second, new deploy gotcha surfaced during DeepEdge's cutover specifically: briefly having both the old service (its Traefik router still on the even-older `expertedge` ID) and the new `deepedge_web` service live simultaneously, both bound to the identical Host(`deepedge.greyin.net`) rule, caused Traefik to non-deterministically round-robin between old and new content -- caught by noticing a freshly-fixed page title inconsistently reappearing as the stale one across repeated requests, not by the service's own health check (which only confirms the new container itself is up, not that the domain has actually stopped flip-flopping) -- fixed by removing the old service immediately, then confirmed with 5 consecutive clean requests before moving on. e2e, run per app after its own full deploy, workers=4/retries=1 against real prod: FlexPro 26/29 own + 22/23 cross-platform; StackWorks 19/19 own + 24/26 cross-platform; DeepEdge 36/44 own + 57/61 cross-platform (1 flaky, passed on retry -- an unrelated duplicate-button UI issue on longlist-future-roles.spec.ts). Every failure across all three apps was individually traced to a confirmed pre-existing, unrelated-to-this-rename cause, not a regression: a subscription-gate test gap on 3 specs that never call grantFreeagentSubscription before posting a gig/session (flexpro-trust-signal.spec.ts, mentor-sessions.spec.ts, mentor-monetization.spec.ts), and a cluster of failures across most of DeepEdge's own suite plus 2 cross-platform specs originally attributed to "a freshly-signed-up candidate's row not reliably showing up yet" -- **this diagnosis was later found wrong** (see the dedicated corrected entry lower on this sheet, 2026-09-04): at least one of the two named cross-platform specs (greyin-score-in-candidate-search.spec.ts) was actually failing on a stale div-tag CSS locator that could never match the page's real `&lt;Link&gt;`-rendered card, nothing to do with data timing; peer-projects.spec.ts's failure was separately traced to an unrelated notFound()-requires-a-candidates-row bug, also since fixed. Not re-investigated further here as out of scope for this row's own naming-rename work. One image-upload.spec.ts failure during FlexPro's own pass was investigated (build-arg baking confirmed correct via direct image inspection) and reported as an unexplained, likely-pre-existing flake rather than claimed fixed. All 7 apps typecheck clean; final platform-wide smoke test after DeepEdge's cutover found every one of the 7 live services on its new codename, all 200s, zero leftover old services.</v>
       </c>
       <c r="D42" t="str">
         <v>User request, 2026-09-02 (FlexPro) through 2026-09-03 (StackWorks, DeepEdge)</v>
@@ -6372,16 +6648,152 @@
         <v>2026-09-03</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Code-vs-database integrity audit: writes to nonexistent columns, and dangling schema</v>
+      </c>
+      <c r="B44" t="str">
+        <v>In progress -- 4 severe live bugs fixed same day; 5 dangling schema objects catalogued, 4 dropped, 1 restored (peer_rater_reliability). List A (9 broken profile-save fields) still open, deliberately deferred pending product review</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Direct user request: "check code vs database integrity - if any where there is code writing to DB table/columns that are not available in any of the schema and if any table/columns exists that are dangling without any code read/write." Built a static-analysis tool (bracket-depth-aware, not pure regex) walking every .from()/.select()/.insert()/.update()/.upsert() call across all 7 apps' full source (539 files), cross-referenced against the live schema pulled directly from information_schema (76 tables + 14 views, 852 columns) rather than trusting migration-file history. Two real tool bugs caught and fixed before trusting any output: a psql field-separator mismatch that emptied the whole schema lookup (everything falsely flagged "unknown"), and a Buffer.from()/upsert-options-argument false-positive source. FOUR live, severe bugs found and confirmed by direct manual verification (not just the tool's say-so) on the writes/reads side: GreyMatters' and Salt &amp; Pepper's entire profile-save feature completely broken for every user (PostgREST rejects a whole UPDATE on any one unknown column, and both routes bundle valid fields with nonexistent ones -- twitter/linkedin were simply misnamed vs. the real twitter_handle/linkedin_url, while email_notifications/show_email/comment_notifications/interests have no column anywhere); FlexPro's own profile-save also completely broken (title/skills/languages/razorpay_account_id -- the first two belong on a different table, candidates, the other two don't exist anywhere); and FlexPro's own homepage "Recently listed" gigs section had silently never rendered for any visitor (price_basic isn't a real gigs column, every other page in the app correctly uses price_min). The three unambiguous 1:1 renames (twitter-&gt;twitter_handle, linkedin-&gt;linkedin_url, price_basic-&gt;price_min) were fixed and deployed same day, verified live (a real ₹1,800/₹2,000/₹1,500-priced gig now renders on the FlexPro homepage where nothing ever had before). The remaining broken fields (email_notifications/show_email/comment_notifications/interests on 2 apps, title/skills/languages/razorpay_account_id on FlexPro) are real product decisions -- drop the dead form fields vs. add real columns vs. redirect to the correct existing table -- deliberately left for a dedicated review rather than guessed at, tracked as List A. On the dangling side, each of the 5 catalogued objects was individually investigated (when added, why dead) before any drop decision, not bulk-assessed: gig_reviews and gig_reviews_view (both from FlexPro's original 001/006-era schema, superseded by order_reviews, a richer redesign with seller-response and reviewee-side stats) were confirmed genuinely dead via both app-code AND migration-function/trigger sweeps to rule out RPC-only access -- a real false-positive source this audit hit for conversations/credit_usage/mentor_session_bookings/rate_limit_attempts, all confirmed live via RPC calls, not dangling -- then dropped via 112_drop_dead_gig_reviews.sql. razorpay_config and payment_analytics (both from 002_razorpay_integration.sql, the platform's original payments scaffolding) were investigated next: razorpay_config's own creation comment says real keys were always meant for env vars, and its payment_capture_mode/currency/receipt_prefix knobs are hardcoded directly in the real checkout code instead -- it held exactly one never-updated placeholder row (webhook_secret='CHANGE_THIS_WEBHOOK_SECRET') since creation; payment_analytics only ever aggregated gig_orders and now predates 8 other razorpay-touching tables the platform has grown since (author_tips, company_subscriptions, flexpro_subscriptions, payout_requests, subscription_plans/tiers/webhooks, razorpay_webhooks) -- not unused-but-still-valid scaffolding, structurally too narrow to be useful as-is even if adopted today. Both dropped via 113_drop_dead_razorpay_config_and_payment_analytics.sql, same verify-before-drop discipline (row counts, FK dependents, view dependents, live function bodies all checked clean immediately beforehand) and the same after-drop discipline (docker service update --force supabase_rest, then a live smoke test across FlexPro/DeepEdge pages, all 200s). peer_rater_reliability is the one exception to "confirmed dead, safe to drop": a genuine regression, not dead-from-birth scaffolding -- 090_peer_rating_anonymity_and_rater_reliability.sql shipped a real "Employer view: rating pattern" anti-collusion panel that peer-projects.spec.ts still asserts on, but the 2026-09-02/03 candidate-detail-page rebuild silently dropped it (that rebuild's own documented scope was 5 different, unrelated specs; this one was never re-checked afterward) -- flagged to the user as worth restoring rather than dropping. RESTORED same day: user confirmed ("restore 5 and do the needful to complete its usage at relevant feature") -- rebuilt the "Peer-confirmed projects" panel on deepedge/candidates/[id]/page.tsx, including the employer/admin-only "Employer view: rating pattern as a peer rater" sub-panel (peer_rater_reliability) and the per-project "⚠ Possible reciprocal rating" badge (peer_project_reciprocity_flags), matching peer-projects.spec.ts's exact assertions. Restoring this surfaced a second, independent bug in the same 2026-09-02/03 rebuild: the page's notFound() gate required a `candidates` table row to exist for the viewed profile, but `candidates` rows are only auto-created for DeepEdge candidate signups (handle_new_user only inserts one when role='candidate') -- any peer-project collaborator tagged from Salt &amp; Pepper/StackWorks/GreyMatters with no DeepEdge candidate profile 404'd outright, which would have made this restored feature untestable and unusable for exactly the cross-pillar collaborators it exists to cover. Fixed by decoupling the page's existence check from `candidates`: it now fetches the target profile directly from `profiles` (404s only if no profile exists at all) and treats `candidates` as optional, gating only its own DeepEdge-specific fields (title, skills, salary, etc.) on the row actually existing. Also found peer-projects.spec.ts itself needed the same grantActiveSubscriptionTier fix already applied to 22 other specs earlier this session (deepedge_hiring credit gating added later than this spec was written) -- added. Verified end to end against real prod: peer-projects.spec.ts passes in full (employer sees the pattern panel, the mutual-pair line, the project, and the reciprocity badge; a non-employer sees the project but neither the panel nor the badge). Regression-checked the 5 other specs this page serves (skill-endorsements, written-recommendations, reference-checks, weekly-digest, greymatters-cross-posting) plus 2 related cross-platform specs -- all still passing; one unrelated pre-existing failure reproduced in greyin-score-in-candidate-search.spec.ts (the separate /candidates search-list page, not this one) -- root-caused and fixed the same day, see the dedicated pending entry below (a stale test locator, not a data-timing issue). Deployed via full rebuild (--build-arg NEXT_PUBLIC_* set, per the known Next.js build-arg gotcha) + docker service update --force greyin-frontend_deepedge_web.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>User request, 2026-09-04</v>
+      </c>
+      <c r="E44" t="str">
+        <v>2026-09-04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Misdiagnosed e2e "propagation timing flake" (greyin-score-in-candidate-search.spec.ts) corrected: real cause was a stale CSS locator, not a data race</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Closed -- fixed and verified passing</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Follow-up "wat next" pass after the peer_rater_reliability restoration above. This spec's failure had been attributed, across two prior write-ups (the internal-rename row above and an earlier session), to "a freshly-signed-up candidate's row not reliably showing up yet on /candidates within the test's timeout" -- a signup-trigger propagation race, deliberately deferred as pre-existing and unrelated to whatever was being worked on each time it was hit. Investigated properly this time rather than deferred again: confirmed via direct psql that the RPC search_verified_candidates() returned the candidate correctly with the right greyin_score; confirmed via a real login (password auth, same JWT the app itself uses) that the RPC returns the candidate under the employer's own real session too, not just as a superuser; confirmed via page.reload() 20+ seconds after all writes settled that the rendered page still showed zero matches for the test's locator; and finally confirmed via the page's own accessibility snapshot (error-context.md) that the candidate's full card, with the correct "Verified Expert - Greyin Score 89" text, was rendered on the page the entire time, first in the list. The test's locator was `div.bg-white.rounded-lg.shadow-md` -- but apps/deepedge/src/app/candidates/page.tsx:199 renders each card as `&lt;Link className="block bg-white rounded-lg shadow-md ..."&gt;`, an anchor element, which a div-tag-qualified CSS selector can never match regardless of any data state. Not a regression from anything recent -- likely stale from whenever this page's card markup last changed shape; the baseline candidates.spec.ts never had this problem because it locates by getByText/name instead of a tag-qualified CSS selector. Fixed by switching to `getByRole('link', { name: ... })`, matching the role/name-locator convention already dominant elsewhere in this suite (e.g. peer-projects.spec.ts). Verified passing on a clean re-run. Spot-checked 10 other specs still using the same `div.bg-white.rounded-lg.shadow-md` pattern (pivoter-mentor, reentry-mentor, stackworks/greyin-score, stackworks/people-directory, saltnpepper/karma-and-anonymous, others) against their own target pages' actual markup -- none of them target DeepEdge's /candidates page, and their own cards are still real `&lt;div&gt;` wrappers, so none share this bug; not changed. Corrected the record in all 3 places the wrong "propagation timing flake" diagnosis had been written down (the internal-rename pending entry above, this entry's own predecessor text, and the project memory files backing both) so a future session doesn't defer this again under a wrong explanation. Having disproven the blanket "timing flake" excuse, ran DeepEdge's full own e2e suite (50 tests) and the full cross-platform project (71 tests) clean to see the REAL current picture rather than trust old numbers. Found and fixed 4 more real, previously-uninvestigated bugs, all confirmed by direct root-cause reads (RLS policies, page markup, or DB state), none guessed at: (1) candidate-profile-credits.spec.ts was navigating to `/candidates/${candidates.id}` instead of `/candidates/${profiles.id}` -- the page's own documented URL-id scheme (profiles.id, not candidates.id) -- so it 404'd before either of its two assertions ever ran, on every single run, unconditionally; fixed to use the already-fetched user id directly, no longer needs the candidates.id lookup at all. (2) ecosystem-search-coverage.spec.ts and (3) greymatters-cross-app-surfacing.spec.ts both used a bare `getByText(/Salt &amp; Pepper/)` / `getByText(/GreyMatters/)` that strict-mode-violates against the shared footer's own identical-text link to that pillar's domain -- fixed by anchoring on each result card's actual accessible text ("Salt &amp; Pepper · discussion", "GreyMatters · post"), which is unambiguous. (4) flexpro-trust-signal.spec.ts -- already a known, named, previously-flagged-but-never-fixed gap ("3 specs never call grantFreeagentSubscription before posting a gig") -- confirmed and fixed by adding the missing grant call; while doing so, found and fixed the SAME root cause independently biting 2 of the other 3 originally-named specs, mentor-sessions.spec.ts and mentor-monetization.spec.ts: `gigs`' own INSERT RLS policy ("An active subscriber can post a gig listing") requires an active flexpro_subscriptions row, which mentor-session creation also needs since it reuses the gigs table (056), but api/mentor-sessions/gigs/route.ts has no pre-check the way /gigs/new's regular flow does -- so a missing grant there fails silently as a generic "Could not create session type" error instead of a helpful /subscribe redirect; added the same grant to both specs, confirmed via psql's pg_policies that this was the exact real cause before touching either file. mentor-monetization.spec.ts now passes clean. DeepEdge's own suite: 50/50 (was reported as 36/44 in an earlier write-up, entirely due to the corrected misdiagnosis above plus these). Cross-platform: all originally-failing specs from this sweep now fixed and passing except one newly-surfaced, genuinely different, NOT-YET-FIXED bug -- mentor-sessions.spec.ts's paid-session path now gets past session-type creation (fixed above) but times out at the mocked-Razorpay checkout's own "Pay &amp; confirm" step (page.waitForURL to /orders/[id] never resolves); confirmed the mock IS in use (mockRazorpayCheckout, not a real-widget flake) so this is a real, separate, unexplored issue in the paid-checkout order-creation path specifically for a mentor-session order type, left open rather than guessed at further -- reported to the user as a new finding rather than chased down in the same pass. ROOT-CAUSED AND FIXED same week: apps/flexpro/src/app/api/orders/create/route.ts unconditionally validated `packageType` against a `{basic: 1, standard: 2, premium: 3}` multiplier map before ever checking whether this was a pre-claimed mentor-session order -- but mentor-sessions/checkout/[orderId]/page.tsx sends `packageType: 'mentor_session'`, not a real multiplier key, so every paid mentor-session checkout 400'd immediately on "Pay &amp; confirm" (the inline script's own `alert('Failed to start payment: ' + data.error)` path), never reaching `new Razorpay(...)`/`.open()` at all -- exactly matching the observed symptom of the button click never resolving to `/orders/[id]`. Confirmed via `book_mentor_slot()` (056_mentor_sessions.sql): the pre-claimed gig_orders row it creates already stores the exact correct `amount` (`COALESCE(gig.price_min, 0)`) at claim time, so no multiplier was ever needed for this path -- the same "trust the pre-claimed order's own amount" design the route's existing `clientJobEngagement` branch (for client-job-application payments) already used. Fixed by adding a third branch, `if (preClaimedOrderId &amp;&amp; !clientJobEngagement)`, mirroring that existing pattern: fetch the pre-claimed order, reject if a Razorpay order was already attached (409, same idempotency guard as clientJobEngagement), create the Razorpay order from the row's own stored amount, attach `razorpay_order_id`. Verified via grep that only the mentor-session checkout page sends `orderId` without `clientJobEngagement` -- the general gig checkout (`checkout/[id]/page.tsx`) never sends an `orderId` field at all (a genuinely new order every time) and the client-job payment page always sets `clientJobEngagement: true`, so neither of those two other flows touches the new branch. mentor-sessions.spec.ts now passes clean; regression-checked checkout-payment.spec.ts, client-jobs.spec.ts, and mentor-monetization.spec.ts (the other 3 specs exercising this same shared route) -- all still pass.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Follow-up during "wat next", 2026-09-04</v>
+      </c>
+      <c r="E45" t="str">
+        <v>2026-09-05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Structural sync pass: dashboard header + ecosystem widget + homepage ecosystem-card section, across all 7 apps</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Done, live and e2e-verified</v>
+      </c>
+      <c r="C46" t="str">
+        <v>User shared two screenshots (a pillar homepage's "Part of the Greyin Ecosystem / One login, five more platforms" card section, and a colored-dot pillar list) and asked to check whether the card bar is consistently available on every pillar landing page, synchronize the *structure* -- not content -- of every landing page and dashboard page across the 7 apps, and add colored dots to the Greyin Hub's own pillar footer list matching the second screenshot. The Hub footer dots were quick and shipped immediately (`greyin-hub/src/components/SiteFooter.tsx`, matching the `w-2 h-2 rounded-full` dot pattern the 6 pillar apps' own footers already use). The larger synchronization task went through EnterPlanMode given its size (14 pages across 7 apps, several real design forks) -- two Explore passes surveyed every app's homepage/dashboard/SiteHeader/EcosystemWidget/NotificationBell, then 3 AskUserQuestion clarifications pinned down scope: (1) force all 7 dashboards onto one lean utility-bar shape rather than leaving greyin-hub/longlist on the heavier public SiteHeader; (2) do NOT invent new stats-bar/feature-grid homepage sections for the 5 apps lacking one -- that would mean fabricating per-app content, not just structure; (3) add the shared EcosystemWidget to all 7 dashboards (previously only on /profile pages + greyin-hub's own dashboard). Executed: dashboard header sync -- 4 apps (stackworks/flexpro/greymatters-blog/saltnpepper-community) already matched the target shape (logo, /feed, notifications, /profile, theme toggle, sign-out) and only needed their hand-rolled bell+own-unread-count-query swapped for the shared self-contained `&lt;NotificationBell /&gt;` component; deepedge was missing /profile + ThemeToggle entirely and had a name/email text block none of the other 4 show, fixed to match; longlist and greyin-hub previously rendered the full public SiteHeader (with Explore/More-Platforms dropdowns) on /dashboard, both switched to the same lean-bar shape -- longlist's omits /feed (no such route exists there), greyin-hub's reduces further to just logo+theme-toggle+sign-out (no /feed, no /profile route -- /dashboard already serves that role there -- and no NotificationBell/notifications-table usage anywhere in Hub's codebase, confirmed by direct grep before deciding not to invent a new notifications system for Hub as part of a "structural sync"). EcosystemWidget added to the 6 dashboards that lacked it, using each app's own `pillar_memberships` query for the `activePillars` prop (TypeScript caught this immediately -- the component requires it, not optional). Homepage ecosystem section: deepedge's one-line text mention (which had also silently gone stale -- it omitted Longlist entirely) was replaced with the same OTHER_PILLARS card-grid section 4 of the other 5 pillar apps already had; longlist had no ecosystem section at all, added net-new in the same position (immediately before the footer) the other apps already use. greyin-hub's homepage was deliberately left alone -- its own bigger pillar grid already IS the ecosystem overview, a difference in kind, not an inconsistency. Deployed all 7 apps (build-arg gotcha applied throughout) and verified live: curl confirmed the correct pillar count/colors render on deepedge and longlist's new sections (including Longlist itself, fixing that staleness), and the dashboard redirect-to-login behavior confirmed for all 3 rebuilt dashboards. A real regression surfaced during e2e verification: swapping the hand-rolled bell for `&lt;NotificationBell /&gt;` changed its accessible-name mechanism from a `title` HTML attribute to `aria-label` -- 8 existing specs across flexpro/deepedge/stackworks/saltnpepper/greymatters used `getByTitle('Notifications')` against exactly the dashboard pages this pass touched (careful not to touch deepedge's separate, untouched /employer/dashboard, which still correctly uses `getByTitle`) -- all 8 fixed to `getByLabel('Notifications')`. One spec (saltnpepper/notifications.spec.ts) showed a genuine, expected, minor behavioral difference: NotificationBell fetches its unread count client-side on mount (a brief empty state before the badge appears) versus the old bar's server-rendered count being present in the very first paint -- confirmed as a real but inherent property of the already-proven-elsewhere shared component (not a new bug) by retrying, which passed; not chased further since the same component has always behaved this way anywhere else it's used (every app's own SiteHeader). All 7 apps' typecheck+build clean throughout; final e2e regression sweep (23 tests across all touched specs) passed, 2 unrelated local-network flakes aside.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>User request, 2026-09-05</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2026-09-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Post-sync visual follow-up: Hub dashboard header reverted to SiteHeader, dashboard-header/preview-banner dark-mode merge fixed, ecosystem-section/footer dark-mode merge fixed (all 7 apps)</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Done, live and e2e-verified</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Direct follow-up after the user reviewed the structural sync pass above against two more screenshots (a pillar homepage's ecosystem-card section, and the Hub's own homepage header) and flagged three concrete visual problems. (1) "greyin hub dashboard looks different than the pillar dashboard pages" -- on reflection the user preferred Hub's dashboard use the SAME header as the rest of the Hub (the pillar-icon-row `&lt;SiteHeader /&gt;`, with its own already-built ThemeToggle + Sign Out), reversing the earlier plan's own choice (approved at the time) to give Hub a shorter custom lean bar since it lacks /feed and /profile routes -- reverted `apps/greyin-hub/src/app/dashboard/page.tsx` from the custom bar back to `&lt;SiteHeader /&gt;`, dropping the now-unused Image/ThemeToggle/LogOut imports built for that bar. (2) "greymatters landing page, gap needed between 5 pillar bar and footer" -- checking another pillar app's dark-mode screenshot first confirmed this was universal, not greymatters-specific: the ecosystem-card section's `dark:bg-gray-900` happened to exactly equal the footer's own fixed (theme-invariant) `bg-gray-900`, so in dark mode the two sections shared one solid color with only a barely-visible 1px border between them -- looked like a single merged block despite real padding being present. Fixed across all 6 apps using this section (stackworks/flexpro/greymatters-blog/saltnpepper-community/deepedge/longlist) by changing the section's dark background to `dark:bg-gray-950`, matching the page's own base background instead of the footer's -- the footer now visibly pops against a slightly darker section above it, the same depth-based separation that already worked correctly in light mode (white section vs. dark footer). (3) "preview build notice merging with pillar dashboard header in dark theme" -- same root shape of bug: every dashboard's hand-rolled header bar used `dark:bg-gray-900`, identical to the preview banner's own fixed `bg-gray-900`, while `SiteHeader.tsx` (used everywhere else) already correctly uses `dark:bg-gray-950` -- confirmed this was exclusively a dashboard-header issue via grep before touching anything. Fixed the same 6 dashboard headers (deepedge's is a `&lt;nav&gt;`, the other 5 are `&lt;header&gt;`) to `dark:bg-gray-950` (+ an explicit `dark:border-gray-800`, matching SiteHeader's own border treatment, on the 5 that lacked one). All fixes verified with real dark-mode screenshots (localStorage `greyin:theme=dark` + reload) before and after, not just code inspection -- confirmed the exact merge reported in each screenshot, then confirmed each fix visually resolved it. All 7 apps typecheck+build clean; e2e regression sweep (dashboard-activity/gig-quality, header-auth-state, longlist-activity, greyin-hub homepage -- 15 tests) passed, 1 unrelated local-network flake aside.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>User request, 2026-09-05</v>
+      </c>
+      <c r="E47" t="str">
+        <v>2026-09-05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Second visual follow-up: redundant Dashboard link on Hub, EcosystemWidget single-row layout, pillar dashboard-bar icon/color/label consistency</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Done, live and e2e-verified</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Third round of the same visual-polish thread. (1) "dashboard link not needed again on greyin hub dashboard" -- since Hub's dashboard now uses `&lt;SiteHeader /&gt;` (reverted in the prior round), it showed a "Dashboard" nav link even while already on /dashboard; fixed by adding `usePathname()` to `greyin-hub/src/components/SiteHeader.tsx` and hiding that one link (desktop + mobile nav) when `pathname === '/dashboard'` -- every other page keeps the link. (2) "'Your Greyin Ecosystem' status can be 6 block in single row instead of 3x2" -- `EcosystemWidget.tsx`'s grid was `grid-cols-1 sm:grid-cols-2` (2-wide, horizontal icon-left cards with a full description line); changed to `grid-cols-2 sm:grid-cols-3 lg:grid-cols-6` with a shorter vertical card (dot on top, name, "Active"/"Visit to join") so 6 fit in one row at desktop width -- applied identically across all 7 apps' copies of this file (no shared package; hand-duplicated per this platform's established convention). (3) "each pillar landing page header must have same pillar icon used on greyin landing page... no need of dashboard next to pillar name and sync color" -- investigated concretely rather than guessed: greyin-hub's SiteHeader.tsx has a canonical PILLAR_ICONS map (deepedge=Building2, greymatters=BookOpen, saltnpepper=Users, flexpro=Briefcase, stackworks=FlaskConical, longlist=Telescope) and every pillar app's own SiteHeader.tsx already imports and uses this exact same icon for its own logo -- marketing/landing headers were already correct. The actual mismatch was in each app's separate, hand-rolled DASHBOARD bar (not SiteHeader): deepedge's had no icon at all (plus a stray "Dashboard" text label neither the user's screenshot nor any other app's bar has, and used text-blue-600 despite deepedge's real brand color being indigo everywhere else -- homepage, buttons, everything); flexpro's dashboard bar used a Package icon instead of Briefcase; greymatters-blog's used PenTool instead of BookOpen; and flexpro/greymatters-blog/saltnpepper-community's dashboard-bar app-name text all used a generic text-indigo-600 regardless of the app's own real accent (confirmed via each app's own homepage hero classes: flexpro=orange, greymatters=sky, saltnpepper=purple -- a genuine pre-existing copy-paste bug, not a deliberate choice). Fixed all of it: deepedge's bar gets a Building2 icon + indigo color + the "Dashboard" label removed; flexpro's gets Briefcase + orange; greymatters-blog's gets BookOpen + sky; saltnpepper-community's gets purple (icon was already correct, Users); stackworks (FlaskConical/teal) and longlist (Telescope/amber) needed no change, already correct. All 7 apps typecheck+build clean; e2e regression sweep (deepedge homepage/auth/notification-bell, greyin-hub homepage, dashboard-activity-and-gig-quality, header-auth-state -- 18 tests) passed clean, no flakes.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>User request, 2026-09-05</v>
+      </c>
+      <c r="E48" t="str">
+        <v>2026-09-05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Platform-wide pillar icon/color consistency sweep: 39 files across deepedge, flexpro, greymatters-blog</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Done, live and e2e-verified</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Direct follow-up to the second visual-polish round above -- user asked, via a "wat next" AskUserQuestion, to sweep for more of the same copy-paste icon/color bug found in dashboard bars. Delegated the search to an Explore agent (read-only, no edits) checking every hand-rolled header across all 7 apps -- employer-dashboard variants, admin pages, login/signup/verify/reset-password, and any other page rendering its own logo outside the shared SiteHeader/SiteFooter/dashboard-bar components already fixed. Confirmed each app's own SiteHeader.tsx was already correct everywhere (imports and uses the right icon from the canonical PILLAR_ICONS map) -- the drift was isolated to standalone pages that each hand-roll their own header instead of using SiteHeader. Found real, live bugs in 3 apps, spot-verified directly (not just trusting the agent) before any edit: deepedge -- 17 files used `Briefcase` instead of the canonical `Building2` icon (a stray leftover, likely from an early shared template), 4 more files (dashboard/applications, jobs/[id]/apply, feed, companies/[id]) additionally used `text-blue-600` instead of deepedge's real indigo, and 4 employer/* pages (settings, post-job, jobs/[id]/applications, jobs/[id]/edit) had no icon at all, just bare text. flexpro -- 11 files used `text-blue-600` or, in the mentor-sessions/* pages, `text-indigo-600`, instead of flexpro's real orange (confirmed via flexpro's own homepage hero classes before touching anything -- this is a genuine brand-color bug, not a deliberate choice, matching the exact same pattern already found and fixed in dashboard bars the round before). greymatters-blog -- 11 files used `text-blue-600` instead of its real sky-blue, same pattern. Every file with more than one matching color string was individually inspected before editing (not blindly sed'd) since several admin pages reuse the same blue on an unrelated ShieldCheck/Sparkles icon elsewhere on the page that was correctly left untouched -- only the logo instance, inside the `&lt;a href="https://greyin.net"&gt;` block, was changed in those files; files confirmed to have exactly one clean occurrence (import + single JSX use, no icon reused elsewhere, no pre-existing conflicting import) were fixed via scoped sed, the rest via individual Edit calls. stackworks, longlist, and saltnpepper-community were confirmed fully clean by the same sweep -- no changes needed there. All 3 touched apps typecheck+build clean, deployed live, and e2e-verified: 104/106 tests passed across deepedge+flexpro+greymatters' full own suites, the only 2 failures being `image-upload.spec.ts` in flexpro and greymatters -- at the time believed a pre-existing, previously-flagged-but-never-investigated flake unrelated to this change; **root-caused and fixed the same week, see the dedicated entry below** -- it was a stale test locator, not a real flake.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>User request, 2026-09-05</v>
+      </c>
+      <c r="E49" t="str">
+        <v>2026-09-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>List A resolved: 9 broken profile-save fields across GreyMatters/Salt &amp; Pepper/FlexPro, deferred from the DB-integrity audit</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Done, live and e2e-verified</v>
+      </c>
+      <c r="C50" t="str">
+        <v>User asked to resume List A -- the product decisions deliberately deferred from the 2026-09-04 integrity audit (see that pending entry). Before proposing anything, checked whether any code anywhere actually consumes each broken field (email sends, public display, matching/search) and what real infrastructure already exists elsewhere on the platform, then presented per-field recommendations with reasoning; user approved proceeding with all of them. GreyMatters' email_notifications/show_email and Salt &amp; Pepper's email_notifications/comment_notifications: confirmed fully inert (no email-sending code anywhere, no display logic reads show_email) -- dropped the UI entirely (removed the checkboxes and their whole now-empty "Writing Preferences"/"Notification Preferences" sections) rather than add dead columns, since building real functionality would mean building an outbound email system this platform has already deliberately avoided (SMTP rate-limit issue; the weekly digest was built in-app for the same reason). Salt &amp; Pepper's "interests" (confirmed unread anywhere, but plausible community-directory value, cheap to add): added a real text[] column (migration 114). FlexPro's "title" (its own generic professional title, distinct from candidates.current_title which is DeepEdge's current-employer-title concept) and "languages": added real columns (114). FlexPro's "skills": redirected to the existing, already-platform-wide profile_skills table (confirmed live via skill_endorsements/skill_ratings, and already synced into from DeepEdge's candidates.skills via a trigger) instead of a new profiles column -- full-replace semantics on save (delete skills no longer listed, add new ones), confirmed safe since skill_endorsements.skill is a plain text match, not an FK, so removing a skill never cascades or destroys endorsement history. FlexPro's "razorpay_account_id": confirmed a separate, real payout_requests table (bank_account_name/number/ifsc + Razorpay-X fields) already handles payouts via a working /earnings page -- dropped the dead field entirely rather than wire up a second, redundant payout path. Two more real bugs found while building e2e coverage for this (no profile-save spec existed for any of these 3 apps before now, which is exactly how they stayed silently broken): GreyMatters and Salt &amp; Pepper's profile pages both read back the OLD, wrong field names for their own already-fixed columns from the 2026-09-04 audit (profile?.twitter instead of profile?.twitter_handle; profile?.linkedin instead of profile?.linkedin_url) -- the write side had been corrected that day but the read/display side never was, so a save silently succeeded while the form kept showing blank/stale values on every reload. Fixed both. Added a new profile-update.spec.ts per app (3 total, all previously absent) covering the exact fields that used to be silently dropped; FlexPro's additionally exercises the profile_skills full-replace round-trip (add two skills, save, reload; remove one, save, reload, confirm only the remaining one persists). All 3 apps typecheck+build clean, deployed live. Also fixed, found in the same e2e pass: a 4th spec (saltnpepper/mentor-session-link.spec.ts, cross-app) hit the exact same "gigs' INSERT RLS requires an active flexpro_subscriptions row, mentor-session creation has no pre-check" gap already fixed in 2 other specs earlier the same week -- same fix applied, confirmed via grep that no other spec creating a mentor-session gig was still missing it. Full regression sweep across all 3 apps' own suites (82 tests) passed clean except 2 -- at the time believed pre-existing, already-documented, unrelated flakes (image-upload.spec.ts in flexpro/greymatters, root-caused and fixed the same week, see the dedicated entry below) -- and 1 pre-existing flaky pass-on-retry (karma-and-anonymous.spec.ts), unrelated.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>User request, 2026-09-05</v>
+      </c>
+      <c r="E50" t="str">
+        <v>2026-09-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>image-upload.spec.ts (flexpro + greymatters) root-caused: a stale test locator, not a real flake -- had been flagged as an unexplained pre-existing failure across at least 3 separate sessions/passes without ever being investigated</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Done, fixed, verified passing</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Follow-up "wat next" pass -- swept memory for anything still flagged-but-never-actually-investigated (the same discipline that found SEC-040) and found this: `image-upload.spec.ts` had failed in every regression sweep this session touched flexpro or greymatters (at least 4 separate runs across different unrelated passes), each time waved off as "a known, previously-documented pre-existing flake" without anyone actually looking at why. Investigated properly instead of deferring again: added temporary diagnostic logging (the real hidden `image_url` value at submit time, the real `&lt;img&gt;` src rendered on the published page) rather than guessing, and found the upload pipeline was never broken at all -- the client-side upload succeeds, the DB write succeeds (confirmed via direct query), the display page renders the real image correctly. The ONLY problem was the test's own locator: `ImageUploader.tsx` (identical in both apps) nests every upload under the uploader's own `user.id` before the folder name (`${user.id}/${folder}/...`), so the real storage path is `public-images/&lt;userId&gt;/gig-images/&lt;file&gt;` (or `.../post-covers/&lt;file&gt;` for greymatters) -- not `public-images/gig-images/` or `public-images/post-covers/` adjacent, which both tests' locators incorrectly assumed and could never match regardless of whether the upload itself worked, ever, since the day these tests were written. Fixed both locators to match on the actual unique folder segment (`/gig-images/`, `/post-covers/`) instead of assuming adjacency to the bucket name. Verified via direct diagnostic capture of the real production URL before fixing (not just "it passes now") -- confirmed the real shape once, then fixed and re-verified passing, stable across repeated runs. Grepped for any other spec assuming the same wrong adjacency -- none found, these were the only two. Lesson for this codebase: a test failure chalked up to "known pre-existing flake" across multiple sessions without ever being opened once is exactly the kind of debt that compounds silently -- this one had zero connection to whatever each session was actually working on each time it was seen, which is precisely why it kept getting deferred instead of fixed.</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Follow-up during "wat next", 2026-09-05</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-09-05</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -7675,9 +8087,41 @@
         <v>Tightened (090) to USING(auth.uid()=rater_id OR employer/admin) before this feature was ever deployed to any real user -- a regular member now sees only ratings they personally gave; nobody else's, at the RLS layer itself, not by app convention. Employers/admins get purpose-built aggregate views instead (peer_rater_reliability, peer_project_reciprocity_flags), each independently gated via their own EXISTS(...role IN (employer,admin)) clause baked into the view's WHERE, since the tightened base-table policy alone no longer exposes rows broadly enough for an aggregate view to rely on. Verified via direct RLS simulation as rater/non-rater/employer/admin (all four cases: own-rating visible, others'-rating hidden, employer aggregate visible, non-employer aggregate empty) and end-to-end via peer-projects.spec.ts.</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SEC-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Privacy</v>
+      </c>
+      <c r="C41" t="str">
+        <v>HIGH</v>
+      </c>
+      <c r="D41" t="str">
+        <v>collaborators view lost security_invoker=true when 089_peer_projects.sql recreated it (CREATE OR REPLACE VIEW does not preserve reloptions from the version it replaces), reverting to Postgres's default security_definer-like behavior under the view owner (postgres) -- combined with anon holding PostgREST's standard SELECT grant on every view, this meant the underlying tables' RLS (project_applications/project_asks/gig_orders/peer_project_members, each scoped to the specific applicant/owner/buyer/seller/peer-member) was not enforced at all when queried through this view.</v>
+      </c>
+      <c r="E41" t="str">
+        <v>deployment/migrations/067_security_critical_fixes.sql (original security_invoker=true setting); 089_peer_projects.sql (the CREATE OR REPLACE VIEW that silently dropped it). Flagged, not fixed, during the 2026-08-31 freeagent-&gt;flexpro rename (found incidentally while checking view reloptions before an unrelated migration) -- sat open for days.</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Confirmed live and exploitable before fixing, not theoretical: a plain unauthenticated curl (public anon key only, zero login) against /rest/v1/collaborators?select=*&amp;limit=5 returned real cross-user, cross-pillar collaboration pairs (user_id/collaborator_id/pillar/occurred_at) platform-wide -- anyone could enumerate every "who has worked with whom" pairing across StackWorks/FlexPro/peer-projects with no account at all.</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="H41" t="str">
+        <v>2026-08-31 (flagged)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>2026-09-05</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Re-applied security_invoker=true via 115_fix_collaborators_security_invoker.sql. Before touching anything, checked all 5 real call sites in the codebase (greyin-hub/dashboard, stackworks/people, saltnpepper-community/members, deepedge/candidates/[id], flexpro/sellers/[id]) -- every one filters .eq('user_id', &lt;the current authenticated viewer's own id&gt;), so in every legitimate row the viewer IS one of the two collaborating parties, exactly what each underlying table's own RLS already permits for its applicant/owner/buyer/seller/peer-member; the fix could not break any real usage. Verified via the identical unauthenticated curl immediately after (now returns []), and via the full set of specs that exercise this view's real functionality end to end (skill-endorsements, written-recommendations, peer-projects, worked-together on StackWorks, and worked-together-surfacing.spec.ts specifically -- which asserts both that real collaborators see each other AND that "a stranger sees neither") -- all 5 passed clean. Added a permanent regression guard to security-regressions.spec.ts (a plain unauthenticated request against /rest/v1/collaborators must always return zero rows) so this can never silently regress again the way it did for over a week the first time.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/greyin-requirements-traceability.xlsx
+++ b/docs/greyin-requirements-traceability.xlsx
@@ -6126,16 +6126,16 @@
         <v>Explainable AI match rationale</v>
       </c>
       <c r="B13" t="str">
-        <v>Not built -- AI moat roadmap item</v>
+        <v>Done</v>
       </c>
       <c r="C13" t="str">
-        <v>For every AI-Verified Search result or Longlist match, generate a plain-language "why this candidate/match" explanation alongside the score. Not cosmetic: NYC Local Law 144 and the EU AI Act's high-risk classification for hiring AI both push toward mandatory explainability for AI hiring tools -- this is a compliance requirement an enterprise buyer's legal team will increasingly ask about, not just a UX nicety. Would extend llm_feature_flags/the existing complete() call sites (048) rather than a new subsystem</v>
+        <v>Longlist's AI-surfaced candidate matching (lib/match-candidates.ts) already carried a per-match `reason` field, rendered on the employer's role-candidates page -- this roadmap item's framing predated realizing that half was already shipped. The real gap was "AI-Verified Search" (the cross-app person search on deepedge/stackworks/flexpro/greymatters-blog/saltnpepper-community): it had no per-result explanation at all, just a Greyin Score badge. Closed 2026-09-05 by adding explainPersonMatch() to each app's parse-search-query.ts -- deliberately deterministic, not a second LLM call: parseSearchQuery only extracts structured filters, it doesn't rank/score people, so the honest answer to "why did this result appear" is exactly which filter (keyword/skill match, min_verified_outcomes threshold, availability, location) this person actually satisfied. A transparent, auditable reason is also the more defensible answer under NYC Local Law 144 / the EU AI Act than a fabricated-sounding LLM narrative would have been. Shown as a "Matched: ..." line on every person result across all 5 apps. Verified by an added assertion in nl-search.spec.ts</v>
       </c>
       <c r="D13" t="str">
-        <v>Pitch-deck AI moat review, 2026-09-01</v>
+        <v>Pitch-deck AI moat review, 2026-09-01; built 2026-09-05</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-05</v>
       </c>
     </row>
     <row r="14">
@@ -6143,16 +6143,16 @@
         <v>Bias/fairness auditing on AI matching output</v>
       </c>
       <c r="B14" t="str">
-        <v>Not built -- AI moat roadmap item</v>
+        <v>Done</v>
       </c>
       <c r="C14" t="str">
-        <v>A stated, active commitment to monitor AI-Verified Search and Longlist AI matching for skew against protected characteristics, not just a policy statement. Consistent with the platform's existing ethos -- the LinkedIn-style unverified-connection model was explicitly rejected on ethical grounds this session in favor of the collaborators-gated model. Large enterprise AI procurement increasingly requires a bias audit before signing; committing to this now is a real differentiator, not aspiration for its own sake</v>
+        <v>Real disparate-impact measurement needs demographic data, which the platform had never collected -- explicit user decision 2026-09-05: add optional, self-disclosed fields (standard EEO-survey pattern: gender/age_range/disability_status, always includes "prefer not to say"), kept in a dedicated profile_demographics table (119) with no admin SELECT policy at all, never shown to employers, never used as a matching input. Longlist's AI candidate matching (lib/match-candidates.ts) now also writes to a new append-only ai_match_audit_log (also no direct SELECT access for anyone) every time it surfaces someone, since that call was previously live/ephemeral with no history to audit at all. get_bias_audit_report() (admin-only SECURITY DEFINER function) computes a standard EEOC "four-fifths rule" comparison -- each gender bucket's share of eligible people vs. its share of actual AI-surfaced matches, flagging any bucket selected at under 80% of the best-performing bucket's rate -- and can only ever return aggregate per-bucket counts, never a row traceable to one person. Surfaced at greyin-hub's /admin/bias-audit. Self-ID collection UI lives on Longlist's own /profile (the app whose AI matching is being audited). Verified end to end by bias-audit.spec.ts, which also caught and fixed a real bug in the first version of get_bias_audit_report() (120: a RETURNS TABLE OUT-parameter named `bucket` collided with an unqualified column reference of the same name inside one CTE, a classic PL/pgSQL ambiguity)</v>
       </c>
       <c r="D14" t="str">
-        <v>Pitch-deck AI moat review, 2026-09-01</v>
+        <v>Pitch-deck AI moat review, 2026-09-01; scoping decision + built 2026-09-05</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-05</v>
       </c>
     </row>
     <row r="15">
@@ -6160,16 +6160,16 @@
         <v>AI-powered mentor matching (Coaching)</v>
       </c>
       <c r="B15" t="str">
-        <v>Not built -- AI moat roadmap item</v>
+        <v>Done</v>
       </c>
       <c r="C15" t="str">
-        <v>Suggest best-fit mentors by seniority gap, stated goals (future_interests, 087), and session-rating history -- a natural extension of data already collected, directly strengthening Coaching, one of the three Primary revenue tiers, not just the platform generally. Would reuse the existing complete()/llm_feature_flags pattern (048) and the mentor_sessions schema (056, 062)</v>
+        <v>FlexPro's /mentor-sessions listing (118, lib/mentor-match.ts) now shows an optional "Recommended for you" section above the full unfiltered listing when the viewer is logged in with future_interests (087) set and there are 2+ active mentor-session gigs to rank -- a live, per-request LLM call (same real-time posture as parse-search-query.ts's NL search, not a new stored-recommendation subsystem) ranks gigs against the viewer's stated interests plus each mentor's existing seller_rating/total_reviews as a session-rating-history signal, returning strict JSON picks mapped back to real gig rows by index (never trusting a model-returned id). Purely additive -- the full listing is unchanged and always shown. Verified end to end (two gigs on clearly different topics, a viewer whose stated interests match one of them) by ai-mentor-matching.spec.ts</v>
       </c>
       <c r="D15" t="str">
-        <v>Pitch-deck AI moat review, 2026-09-01</v>
+        <v>Pitch-deck AI moat review, 2026-09-01; built 2026-09-05</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-05</v>
       </c>
     </row>
     <row r="16">
@@ -6177,16 +6177,16 @@
         <v>AI-synthesized reference reports</v>
       </c>
       <c r="B16" t="str">
-        <v>Not built -- AI moat roadmap item</v>
+        <v>Done</v>
       </c>
       <c r="C16" t="str">
-        <v>An AI summarization layer over the existing structured references/reference_requests/reference_responses tables (065) -- turning multiple raw referee responses into one consistency-flagged report for the requesting employer, saving real review time. Small, credible extension of live data, not a new data model</v>
+        <v>An AI summarization layer over the existing structured references/reference_requests/reference_responses tables (065) -- once an employer has 2+ referee responses for the same candidate, a local-model synthesis (117, lib/reference-synthesis.ts) runs automatically on the next response submission and produces one consistency-flagged report (consistent | notable_differences) shown on the employer's candidate detail page, above the raw responses. Reuses the existing complete()/llm_feature_flags pattern (048); confidential to the requesting employer only, same as the raw responses it summarizes -- the candidate never sees it. Covered by ai-reference-synthesis.spec.ts (asserts no report with 1 response, report appears with 2)</v>
       </c>
       <c r="D16" t="str">
-        <v>Pitch-deck AI moat review, 2026-09-01</v>
+        <v>Pitch-deck AI moat review, 2026-09-01; built 2026-09-05</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-05</v>
       </c>
     </row>
     <row r="17">
